--- a/Customer support excel dashboard.xlsx
+++ b/Customer support excel dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/43876654085fa34b/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E8478D8-E7FF-44B4-9B11-39FA6FA130F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="8_{4E8478D8-E7FF-44B4-9B11-39FA6FA130F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED11B9E1-24AF-4D03-8EA0-962452841033}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
@@ -3466,7 +3466,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="168" formatCode="&quot;₹&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3509,18 +3509,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF002060"/>
-      <name val="Berlin Sans FB Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF002060"/>
-      <name val="Berlin Sans FB"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Berlin Sans FB Demi"/>
@@ -3539,7 +3527,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3554,7 +3542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3715,11 +3715,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -3752,8 +3753,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3767,27 +3766,29 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="13" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="20% - Accent3" xfId="2" builtinId="38"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -4096,10 +4097,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="dk1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4107,32 +4105,27 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN">
+              <a:rPr lang="en-IN" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="002060"/>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t>Call</a:t>
+              <a:t>Call count per month</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-IN" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="002060"/>
-                </a:solidFill>
-                <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t> count per month</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-IN">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-              <a:latin typeface="Berlin Sans FB Demi" panose="020E0802020502020306" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.27192594653961677"/>
+          <c:y val="3.5182185545860119E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4148,10 +4141,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -4491,36 +4481,12 @@
       <c:pivotFmt>
         <c:idx val="4"/>
         <c:spPr>
-          <a:gradFill flip="none" rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="95000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="20000"/>
-                  <a:lumOff val="80000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="30000"/>
-                  <a:lumOff val="70000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="1"/>
-            <a:tileRect/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:ln>
             <a:solidFill>
               <a:schemeClr val="accent1">
@@ -4552,10 +4518,7 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="dk1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -4595,7 +4558,10 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
@@ -4623,10 +4589,7 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="dk1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -4668,36 +4631,12 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:gradFill flip="none" rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="5000"/>
-                    <a:lumOff val="95000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="95000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="30000"/>
-                    <a:lumOff val="70000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="1"/>
-              <a:tileRect/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:ln>
               <a:solidFill>
                 <a:schemeClr val="accent1">
@@ -4759,40 +4698,40 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>15</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>8</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4848,7 +4787,10 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
@@ -4909,40 +4851,40 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>15</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>8</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4998,10 +4940,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="dk1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5057,10 +4996,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="dk1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5075,15 +5011,24 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:lumMod val="75000"/>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
         <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -5098,21 +5043,43 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:noFill/>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:srgbClr val="002060"/>
       </a:solidFill>
-      <a:round/>
+      <a:prstDash val="solid"/>
+      <a:miter lim="800000"/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -5246,10 +5213,7 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -5306,10 +5270,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -5532,25 +5493,25 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>34</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>23</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>25</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5725,14 +5686,28 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:srgbClr val="002060"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -5858,7 +5833,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="85000"/>
+                <a:lumMod val="95000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -5997,30 +5972,12 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:gradFill flip="none" rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="22000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="60000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="97000"/>
-                    <a:lumOff val="3000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="85000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="1"/>
-              <a:tileRect/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -6040,10 +5997,10 @@
                   <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>#N/A</c:v>
+                  <c:v>207</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>186</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>#N/A</c:v>
@@ -6186,14 +6143,28 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:srgbClr val="002060"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -6303,9 +6274,7 @@
           <c:order val="0"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="bg1">
-                <a:lumMod val="85000"/>
-              </a:schemeClr>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
             <a:ln>
               <a:solidFill>
@@ -6443,29 +6412,12 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:gradFill>
-              <a:gsLst>
-                <a:gs pos="22000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="60000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="97000"/>
-                    <a:lumOff val="3000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="85000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="1"/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -6485,10 +6437,10 @@
                   <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>#N/A</c:v>
+                  <c:v>20872</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16651</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>#N/A</c:v>
@@ -6606,14 +6558,28 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:srgbClr val="002060"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -7148,7 +7114,8 @@
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent1">
-              <a:lumMod val="75000"/>
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:ln>
@@ -7204,9 +7171,8 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="tx2">
-              <a:lumMod val="40000"/>
-              <a:lumOff val="60000"/>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:ln>
@@ -7282,7 +7248,8 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1">
-                <a:lumMod val="75000"/>
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -7404,9 +7371,8 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="tx2">
-                <a:lumMod val="40000"/>
-                <a:lumOff val="60000"/>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -7622,14 +7588,28 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:srgbClr val="002060"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -7858,30 +7838,12 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
-          <a:gradFill flip="none" rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="48000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="40000"/>
-                  <a:lumOff val="60000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="1"/>
-            <a:tileRect/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:ln>
             <a:solidFill>
               <a:schemeClr val="accent1">
@@ -7958,30 +7920,12 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:gradFill flip="none" rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="48000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="40000"/>
-                    <a:lumOff val="60000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="1"/>
-              <a:tileRect/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:ln>
               <a:solidFill>
                 <a:schemeClr val="accent1">
@@ -7994,22 +7938,25 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivots '!$K$34:$K$39</c:f>
+              <c:f>'Pivots '!$K$34:$K$40</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:strCache>
@@ -8017,24 +7964,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivots '!$L$34:$L$39</c:f>
+              <c:f>'Pivots '!$L$34:$L$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>70</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>62</c:v>
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8179,14 +8129,28 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:srgbClr val="002060"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -11785,8 +11749,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="838200" y="431800"/>
-          <a:ext cx="1066800" cy="660400"/>
+          <a:off x="833664" y="868589"/>
+          <a:ext cx="1072243" cy="652236"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12018,8 +11982,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1149350" y="914400"/>
-          <a:ext cx="495300" cy="165100"/>
+          <a:off x="1147536" y="1345746"/>
+          <a:ext cx="498021" cy="162379"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12068,7 +12032,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>186</a:t>
+            <a:t>207</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1100" b="0">
             <a:solidFill>
@@ -12400,7 +12364,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>16,651</a:t>
+            <a:t>20,872</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1100" b="1">
             <a:solidFill>
@@ -12723,7 +12687,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>17,807</a:t>
+            <a:t>17,700</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1100" b="1">
             <a:solidFill>
@@ -13399,7 +13363,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>62</a:t>
+            <a:t>60</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1100" b="1">
             <a:solidFill>
@@ -13415,15 +13379,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>102634</xdr:colOff>
+      <xdr:colOff>45939</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>60196</xdr:rowOff>
+      <xdr:rowOff>37517</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>463526</xdr:colOff>
+      <xdr:colOff>215447</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>145686</xdr:rowOff>
+      <xdr:rowOff>123007</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -13459,8 +13423,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11855907" y="4193469"/>
-              <a:ext cx="1584710" cy="1748035"/>
+              <a:off x="11793439" y="4108321"/>
+              <a:ext cx="1394151" cy="1718347"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -13530,16 +13494,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>99785</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>7711</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>167569</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>204107</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11340</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13574,8 +13538,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>311208</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>521607</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>36306</xdr:rowOff>
     </xdr:to>
@@ -13607,15 +13571,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>317500</xdr:colOff>
+      <xdr:colOff>113394</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>11759</xdr:rowOff>
+      <xdr:rowOff>23099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>17224</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>113392</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>48065</xdr:rowOff>
+      <xdr:rowOff>45357</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13645,15 +13609,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>438857</xdr:colOff>
+      <xdr:colOff>472874</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>37489</xdr:rowOff>
+      <xdr:rowOff>26151</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>134119</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>36623</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>362857</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>170090</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13682,16 +13646,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>143773</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>642702</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>35943</xdr:rowOff>
+      <xdr:rowOff>1925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>482985</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>544286</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>23276</xdr:rowOff>
+      <xdr:rowOff>34018</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14178,7 +14142,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46136.891616898145" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{D70A1F63-2676-48E0-A490-E8C123280691}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46236.643061574076" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{D70A1F63-2676-48E0-A490-E8C123280691}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="6">
     <cacheField name="[Measures].[Call count]" caption="Call count" numFmtId="0" hierarchy="17" level="32767"/>
@@ -14280,7 +14244,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46136.891620486109" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{3F0B1D00-77BF-4577-9D05-656D673A22DA}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46236.643064814816" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{3F0B1D00-77BF-4577-9D05-656D673A22DA}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="5">
     <cacheField name="[calls].[Representative].[Representative]" caption="Representative" numFmtId="0" hierarchy="3" level="1">
@@ -14555,7 +14519,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46136.89162372685" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{CFFEE625-D966-42EC-A2BC-9488E4A48335}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46236.643067708334" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{CFFEE625-D966-42EC-A2BC-9488E4A48335}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[calls].[Representative].[Representative]" caption="Representative" numFmtId="0" hierarchy="3" level="1">
@@ -14653,12 +14617,12 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46136.891625115742" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{F234545C-1C39-41A2-899B-E44F831E839A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46236.643070486112" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{F234545C-1C39-41A2-899B-E44F831E839A}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="1">
     <cacheField name="[calls].[Representative].[Representative]" caption="Representative" numFmtId="0" hierarchy="3" level="1">
       <sharedItems count="1">
-        <s v="R04"/>
+        <s v="R03"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -14732,12 +14696,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46136.891628124999" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{14D52039-EE49-4129-81D1-7B0929FE0850}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="hera aleem" refreshedDate="46236.64307337963" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{14D52039-EE49-4129-81D1-7B0929FE0850}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Measures].[Call count]" caption="Call count" numFmtId="0" hierarchy="17" level="32767"/>
     <cacheField name="[calls].[Rating rounded].[Rating rounded]" caption="Rating rounded" numFmtId="0" hierarchy="10" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="5">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="5" count="6">
+        <n v="0"/>
         <n v="1"/>
         <n v="2"/>
         <n v="3"/>
@@ -14747,11 +14712,12 @@
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
           <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[calls].[Rating rounded].&amp;[1]"/>
-            <x15:cachedUniqueName index="1" name="[calls].[Rating rounded].&amp;[2]"/>
-            <x15:cachedUniqueName index="2" name="[calls].[Rating rounded].&amp;[3]"/>
-            <x15:cachedUniqueName index="3" name="[calls].[Rating rounded].&amp;[4]"/>
-            <x15:cachedUniqueName index="4" name="[calls].[Rating rounded].&amp;[5]"/>
+            <x15:cachedUniqueName index="0" name="[calls].[Rating rounded].&amp;[0]"/>
+            <x15:cachedUniqueName index="1" name="[calls].[Rating rounded].&amp;[1]"/>
+            <x15:cachedUniqueName index="2" name="[calls].[Rating rounded].&amp;[2]"/>
+            <x15:cachedUniqueName index="3" name="[calls].[Rating rounded].&amp;[3]"/>
+            <x15:cachedUniqueName index="4" name="[calls].[Rating rounded].&amp;[4]"/>
+            <x15:cachedUniqueName index="5" name="[calls].[Rating rounded].&amp;[5]"/>
           </x15:cachedUniqueNames>
         </ext>
       </extLst>
@@ -14885,7 +14851,7 @@
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1">
       <members count="1" level="1">
-        <member name="[calls].[Representative].&amp;[R04]"/>
+        <member name="[calls].[Representative].&amp;[R03]"/>
       </members>
     </pivotHierarchy>
     <pivotHierarchy dragToData="1"/>
@@ -15022,28 +14988,64 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3259E5B2-D58C-468E-8178-45CF2BCFF1C1}" name="REP2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H58:H59" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F91F0398-A766-4D39-9DAF-8DCA9BFC96B4}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="J22:L28" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="1">
-        <item s="1" x="0"/>
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
       </items>
     </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="1">
+  <rowItems count="6">
     <i>
       <x/>
     </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Purchase Amount" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
   <pivotHierarchies count="27">
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -15072,6 +15074,9 @@
   <rowHierarchiesUsage count="1">
     <rowHierarchyUsage hierarchyUsage="3"/>
   </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
@@ -15416,16 +15421,17 @@
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E52C7D3-769B-448D-8BC4-274B535EA91E}" name="rating rep" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="K33:L39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="K33:L40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="5">
+      <items count="6">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
+        <item x="5"/>
       </items>
     </pivotField>
     <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -15433,7 +15439,7 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="7">
     <i>
       <x/>
     </i>
@@ -15448,6 +15454,9 @@
     </i>
     <i>
       <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -15476,7 +15485,7 @@
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1">
       <members count="1" level="1">
-        <member name="[calls].[Representative].&amp;[R04]"/>
+        <member name="[calls].[Representative].&amp;[R03]"/>
       </members>
     </pivotHierarchy>
     <pivotHierarchy dragToData="1"/>
@@ -15525,7 +15534,74 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D1C959F3-8A8E-4743-B237-D7EB516C8898}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3259E5B2-D58C-468E-8178-45CF2BCFF1C1}" name="REP2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H58:H59" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="1">
+        <item s="1" x="0"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="1">
+    <i>
+      <x/>
+    </i>
+  </rowItems>
+  <pivotHierarchies count="27">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="3"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings>
+        <x15:activeTabTopLevelEntity name="[calls]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D1C959F3-8A8E-4743-B237-D7EB516C8898}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="F33:I38" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -15656,114 +15732,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F91F0398-A766-4D39-9DAF-8DCA9BFC96B4}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="J22:L28" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Purchase Amount" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="27">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="3"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="-2"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings>
-        <x15:activeTabTopLevelEntity name="[calls]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A2B34A7-0599-4575-BA47-6532F0EB07E7}" name="daily" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A2B34A7-0599-4575-BA47-6532F0EB07E7}" name="daily" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
   <location ref="F22:G30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -15850,7 +15820,7 @@
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1">
       <members count="1" level="1">
-        <member name="[calls].[Representative].&amp;[R04]"/>
+        <member name="[calls].[Representative].&amp;[R03]"/>
       </members>
     </pivotHierarchy>
     <pivotHierarchy dragToData="1"/>
@@ -15898,7 +15868,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB300512-9F9C-4483-9606-5A10035C3243}" name="monthly" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB300512-9F9C-4483-9606-5A10035C3243}" name="monthly" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A22:C35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -16172,7 +16142,7 @@
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1">
       <members count="1" level="1">
-        <member name="[calls].[Representative].&amp;[R04]"/>
+        <member name="[calls].[Representative].&amp;[R03]"/>
       </members>
     </pivotHierarchy>
     <pivotHierarchy dragToData="1"/>
@@ -16300,9 +16270,9 @@
     <v>Business woman shrugging</v>
   </rv>
   <rv s="0">
-    <v>3</v>
+    <v>2</v>
     <v>4</v>
-    <v>Young businessman writing on notebook</v>
+    <v>Business woman raising hand</v>
   </rv>
 </rvData>
 </file>
@@ -16353,7 +16323,7 @@
         </level>
       </levels>
       <selections count="1">
-        <selection n="[calls].[Representative].&amp;[R04]"/>
+        <selection n="[calls].[Representative].&amp;[R03]"/>
       </selections>
     </olap>
   </data>
@@ -16460,7 +16430,7 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -16519,13 +16489,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -16534,6 +16497,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -56010,19 +55980,19 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="20">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="B10" s="20">
-        <v>16651</v>
+        <v>20872</v>
       </c>
       <c r="C10" s="20">
-        <v>17807</v>
+        <v>17700</v>
       </c>
       <c r="D10" s="20">
-        <v>3.8973118279569863</v>
+        <v>3.8589371980676304</v>
       </c>
       <c r="E10" s="20">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -56052,22 +56022,22 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="22" t="s">
         <v>1049</v>
       </c>
       <c r="B23" s="20">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C23" s="20">
-        <v>10</v>
-      </c>
-      <c r="F23" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="22" t="s">
         <v>1068</v>
       </c>
       <c r="G23" s="20">
-        <v>34</v>
-      </c>
-      <c r="J23" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="22" t="s">
         <v>11</v>
       </c>
       <c r="K23" s="20">
@@ -56078,22 +56048,22 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="22" t="s">
         <v>1050</v>
       </c>
       <c r="B24" s="20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24" s="20">
-        <v>11</v>
-      </c>
-      <c r="F24" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="22" t="s">
         <v>1067</v>
       </c>
       <c r="G24" s="20">
-        <v>29</v>
-      </c>
-      <c r="J24" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="22" t="s">
         <v>9</v>
       </c>
       <c r="K24" s="20">
@@ -56104,22 +56074,22 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="22" t="s">
         <v>1051</v>
       </c>
       <c r="B25" s="20">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" s="20">
-        <v>30</v>
-      </c>
-      <c r="F25" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="22" t="s">
         <v>1064</v>
       </c>
       <c r="G25" s="20">
-        <v>18</v>
-      </c>
-      <c r="J25" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="22" t="s">
         <v>6</v>
       </c>
       <c r="K25" s="20">
@@ -56130,22 +56100,22 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="22" t="s">
         <v>1052</v>
       </c>
       <c r="B26" s="20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" s="20">
-        <v>23</v>
-      </c>
-      <c r="F26" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="22" t="s">
         <v>1063</v>
       </c>
       <c r="G26" s="20">
-        <v>29</v>
-      </c>
-      <c r="J26" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="22" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="20">
@@ -56156,22 +56126,22 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="22" t="s">
         <v>1053</v>
       </c>
       <c r="B27" s="20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="20">
-        <v>22</v>
-      </c>
-      <c r="F27" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="22" t="s">
         <v>1066</v>
       </c>
       <c r="G27" s="20">
-        <v>28</v>
-      </c>
-      <c r="J27" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="22" t="s">
         <v>10</v>
       </c>
       <c r="K27" s="20">
@@ -56182,22 +56152,22 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="22" t="s">
         <v>1054</v>
       </c>
       <c r="B28" s="20">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C28" s="20">
-        <v>11</v>
-      </c>
-      <c r="F28" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="22" t="s">
         <v>1062</v>
       </c>
       <c r="G28" s="20">
-        <v>23</v>
-      </c>
-      <c r="J28" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="22" t="s">
         <v>1048</v>
       </c>
       <c r="K28" s="20">
@@ -56208,70 +56178,70 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="22" t="s">
         <v>1055</v>
       </c>
       <c r="B29" s="20">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C29" s="20">
-        <v>17</v>
-      </c>
-      <c r="F29" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="22" t="s">
         <v>1065</v>
       </c>
       <c r="G29" s="20">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="22" t="s">
         <v>1056</v>
       </c>
       <c r="B30" s="20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" s="20">
-        <v>12</v>
-      </c>
-      <c r="F30" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>1048</v>
       </c>
       <c r="G30" s="20">
-        <v>186</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="22" t="s">
         <v>1057</v>
       </c>
       <c r="B31" s="20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C31" s="20">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="22" t="s">
         <v>1058</v>
       </c>
       <c r="B32" s="20">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C32" s="20">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="22" t="s">
         <v>1059</v>
       </c>
       <c r="B33" s="20">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C33" s="20">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F33" s="21" t="s">
         <v>1042</v>
@@ -56287,14 +56257,14 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="22" t="s">
         <v>1060</v>
       </c>
       <c r="B34" s="20">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C34" s="20">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>1047</v>
@@ -56308,24 +56278,24 @@
       <c r="I34" t="s">
         <v>1048</v>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="22">
+        <v>0</v>
+      </c>
+      <c r="L34" s="20">
         <v>1</v>
       </c>
-      <c r="L34" s="20">
-        <v>3</v>
-      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="22" t="s">
         <v>1048</v>
       </c>
       <c r="B35" s="20">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C35" s="20">
-        <v>186</v>
-      </c>
-      <c r="F35" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="F35" s="22" t="s">
         <v>1002</v>
       </c>
       <c r="G35" s="20">
@@ -56337,15 +56307,15 @@
       <c r="I35" s="20">
         <v>276</v>
       </c>
-      <c r="K35" s="24">
-        <v>2</v>
+      <c r="K35" s="22">
+        <v>1</v>
       </c>
       <c r="L35" s="20">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="22" t="s">
         <v>1001</v>
       </c>
       <c r="G36" s="20">
@@ -56357,15 +56327,15 @@
       <c r="I36" s="20">
         <v>389</v>
       </c>
-      <c r="K36" s="24">
-        <v>3</v>
+      <c r="K36" s="22">
+        <v>2</v>
       </c>
       <c r="L36" s="20">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="22" t="s">
         <v>1000</v>
       </c>
       <c r="G37" s="20">
@@ -56377,15 +56347,15 @@
       <c r="I37" s="20">
         <v>335</v>
       </c>
-      <c r="K37" s="24">
-        <v>4</v>
+      <c r="K37" s="22">
+        <v>3</v>
       </c>
       <c r="L37" s="20">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="22" t="s">
         <v>1048</v>
       </c>
       <c r="G38" s="20">
@@ -56397,19 +56367,27 @@
       <c r="I38" s="20">
         <v>1000</v>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="22">
+        <v>4</v>
+      </c>
+      <c r="L38" s="20">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K39" s="22">
         <v>5</v>
       </c>
-      <c r="L38" s="20">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="K39" s="24" t="s">
+      <c r="L39" s="20">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K40" s="22" t="s">
         <v>1048</v>
       </c>
-      <c r="L39" s="20">
-        <v>186</v>
+      <c r="L40" s="20">
+        <v>207</v>
       </c>
     </row>
     <row r="57" spans="8:16" x14ac:dyDescent="0.35">
@@ -56429,7 +56407,7 @@
       </c>
       <c r="K58" t="str">
         <f>H59</f>
-        <v>R04</v>
+        <v>R03</v>
       </c>
       <c r="L58" t="str" cm="1">
         <f t="array" ref="L58:N62">J23:L27</f>
@@ -56438,7 +56416,7 @@
       <c r="M58">
         <v>189</v>
       </c>
-      <c r="N58" s="25">
+      <c r="N58" s="23">
         <v>18415</v>
       </c>
       <c r="O58" t="e">
@@ -56451,8 +56429,8 @@
       </c>
     </row>
     <row r="59" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H59" s="24" t="s">
-        <v>13</v>
+      <c r="H59" s="22" t="s">
+        <v>6</v>
       </c>
       <c r="L59" t="str">
         <v>R02</v>
@@ -56460,7 +56438,7 @@
       <c r="M59">
         <v>218</v>
       </c>
-      <c r="N59" s="25">
+      <c r="N59" s="23">
         <v>20581</v>
       </c>
       <c r="O59" t="e">
@@ -56479,16 +56457,16 @@
       <c r="M60">
         <v>207</v>
       </c>
-      <c r="N60" s="25">
+      <c r="N60" s="23">
         <v>20872</v>
       </c>
-      <c r="O60" t="e">
+      <c r="O60">
         <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P60" t="e">
+        <v>207</v>
+      </c>
+      <c r="P60">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>20872</v>
       </c>
     </row>
     <row r="61" spans="8:16" x14ac:dyDescent="0.35">
@@ -56498,16 +56476,16 @@
       <c r="M61">
         <v>186</v>
       </c>
-      <c r="N61" s="25">
+      <c r="N61" s="23">
         <v>16651</v>
       </c>
-      <c r="O61">
+      <c r="O61" t="e">
         <f t="shared" si="0"/>
-        <v>186</v>
-      </c>
-      <c r="P61">
+        <v>#N/A</v>
+      </c>
+      <c r="P61" t="e">
         <f t="shared" si="1"/>
-        <v>16651</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="62" spans="8:16" x14ac:dyDescent="0.35">
@@ -56517,7 +56495,7 @@
       <c r="M62">
         <v>200</v>
       </c>
-      <c r="N62" s="25">
+      <c r="N62" s="23">
         <v>20104</v>
       </c>
       <c r="O62" t="e">
@@ -56538,9 +56516,9 @@
       <c r="J65" t="s">
         <v>1076</v>
       </c>
-      <c r="K65" s="43">
+      <c r="K65" s="29">
         <f>A10/A4</f>
-        <v>0.186</v>
+        <v>0.20699999999999999</v>
       </c>
     </row>
     <row r="66" spans="9:16" x14ac:dyDescent="0.35">
@@ -56549,11 +56527,11 @@
       </c>
       <c r="K66">
         <f>_xlfn.XLOOKUP(H59,L58:L62,M58:M62)</f>
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="M66" t="str">
         <f>"% of calls :"&amp;TEXT(K65,"0%")</f>
-        <v>% of calls :19%</v>
+        <v>% of calls :21%</v>
       </c>
       <c r="P66" t="e" vm="6">
         <f>IF(COUNTA(H59:H63)&gt;1,"",_xlfn.XLOOKUP(H59,Assets!E3:E7,Assets!F3:F7))</f>
@@ -56566,11 +56544,11 @@
       </c>
       <c r="K67">
         <f>_xlfn.XLOOKUP(H59,L58:L62,N58:N62)</f>
-        <v>16651</v>
+        <v>20872</v>
       </c>
       <c r="M67" t="str">
         <f>IF(COUNTA(H59:H63)&gt;1,"","call rank:"&amp;K68)</f>
-        <v>call rank:5</v>
+        <v>call rank:2</v>
       </c>
     </row>
     <row r="68" spans="9:16" x14ac:dyDescent="0.35">
@@ -56579,11 +56557,11 @@
       </c>
       <c r="K68">
         <f>_xlfn.RANK.AVG(K66,M58:M62)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M68" t="str">
         <f>IF(COUNTA(H59:H63)&gt;1,"","amount rank:"&amp;K69)</f>
-        <v>amount rank:5</v>
+        <v>amount rank:1</v>
       </c>
     </row>
     <row r="69" spans="9:16" x14ac:dyDescent="0.35">
@@ -56592,7 +56570,7 @@
       </c>
       <c r="K69">
         <f>_xlfn.RANK.AVG(K67,N58:N62)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="9:16" x14ac:dyDescent="0.35">
@@ -56604,427 +56582,427 @@
       </c>
     </row>
     <row r="72" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I72" s="26" t="s">
+      <c r="I72" s="24" t="s">
         <v>1047</v>
       </c>
-      <c r="J72" s="27" t="s">
+      <c r="J72" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K72" s="27" t="s">
+      <c r="K72" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L72" s="27" t="s">
+      <c r="L72" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="M72" s="27" t="s">
+      <c r="M72" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="N72" s="27" t="s">
+      <c r="N72" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O72" s="27" t="s">
+      <c r="O72" s="25" t="s">
         <v>1048</v>
       </c>
-      <c r="P72" s="27"/>
+      <c r="P72" s="25"/>
     </row>
     <row r="73" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I73" s="28" t="s">
+      <c r="I73" s="26" t="s">
         <v>1002</v>
       </c>
-      <c r="J73" s="27"/>
-      <c r="K73" s="27"/>
-      <c r="L73" s="27"/>
-      <c r="M73" s="27"/>
-      <c r="N73" s="27"/>
-      <c r="O73" s="27"/>
-      <c r="P73" s="27"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="25"/>
+      <c r="L73" s="25"/>
+      <c r="M73" s="25"/>
+      <c r="N73" s="25"/>
+      <c r="O73" s="25"/>
+      <c r="P73" s="25"/>
     </row>
     <row r="74" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I74" s="29" t="s">
+      <c r="I74" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="J74" s="30">
+      <c r="J74" s="28">
         <v>891</v>
       </c>
-      <c r="K74" s="30">
+      <c r="K74" s="28">
         <v>1332</v>
       </c>
-      <c r="L74" s="30">
+      <c r="L74" s="28">
         <v>1282</v>
       </c>
-      <c r="M74" s="30">
+      <c r="M74" s="28">
         <v>739</v>
       </c>
-      <c r="N74" s="30">
+      <c r="N74" s="28">
         <v>560</v>
       </c>
-      <c r="O74" s="30">
+      <c r="O74" s="28">
         <v>4804</v>
       </c>
-      <c r="P74" s="27"/>
+      <c r="P74" s="25"/>
     </row>
     <row r="75" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I75" s="29" t="s">
+      <c r="I75" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J75" s="30">
+      <c r="J75" s="28">
         <v>1991</v>
       </c>
-      <c r="K75" s="30">
+      <c r="K75" s="28">
         <v>1886</v>
       </c>
-      <c r="L75" s="30">
+      <c r="L75" s="28">
         <v>1206</v>
       </c>
-      <c r="M75" s="30">
+      <c r="M75" s="28">
         <v>884</v>
       </c>
-      <c r="N75" s="30">
+      <c r="N75" s="28">
         <v>1722</v>
       </c>
-      <c r="O75" s="30">
+      <c r="O75" s="28">
         <v>7689</v>
       </c>
-      <c r="P75" s="27"/>
+      <c r="P75" s="25"/>
     </row>
     <row r="76" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I76" s="29" t="s">
+      <c r="I76" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J76" s="30">
+      <c r="J76" s="28">
         <v>1163</v>
       </c>
-      <c r="K76" s="30">
+      <c r="K76" s="28">
         <v>1180</v>
       </c>
-      <c r="L76" s="30">
+      <c r="L76" s="28">
         <v>1616</v>
       </c>
-      <c r="M76" s="30">
+      <c r="M76" s="28">
         <v>1043</v>
       </c>
-      <c r="N76" s="30">
+      <c r="N76" s="28">
         <v>1747</v>
       </c>
-      <c r="O76" s="30">
+      <c r="O76" s="28">
         <v>6749</v>
       </c>
-      <c r="P76" s="27"/>
+      <c r="P76" s="25"/>
     </row>
     <row r="77" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I77" s="29" t="s">
+      <c r="I77" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="J77" s="30">
+      <c r="J77" s="28">
         <v>1438</v>
       </c>
-      <c r="K77" s="30">
+      <c r="K77" s="28">
         <v>1616</v>
       </c>
-      <c r="L77" s="30">
+      <c r="L77" s="28">
         <v>866</v>
       </c>
-      <c r="M77" s="30">
+      <c r="M77" s="28">
         <v>829</v>
       </c>
-      <c r="N77" s="30">
+      <c r="N77" s="28">
         <v>2070</v>
       </c>
-      <c r="O77" s="30">
+      <c r="O77" s="28">
         <v>6819</v>
       </c>
-      <c r="P77" s="27"/>
+      <c r="P77" s="25"/>
     </row>
     <row r="78" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I78" s="28" t="s">
+      <c r="I78" s="26" t="s">
         <v>1001</v>
       </c>
-      <c r="J78" s="27"/>
-      <c r="K78" s="27"/>
-      <c r="L78" s="27"/>
-      <c r="M78" s="27"/>
-      <c r="N78" s="27"/>
-      <c r="O78" s="27"/>
-      <c r="P78" s="27"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+      <c r="L78" s="25"/>
+      <c r="M78" s="25"/>
+      <c r="N78" s="25"/>
+      <c r="O78" s="25"/>
+      <c r="P78" s="25"/>
     </row>
     <row r="79" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I79" s="29" t="s">
+      <c r="I79" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="J79" s="30">
+      <c r="J79" s="28">
         <v>1233</v>
       </c>
-      <c r="K79" s="30">
+      <c r="K79" s="28">
         <v>223</v>
       </c>
-      <c r="L79" s="30">
+      <c r="L79" s="28">
         <v>1680</v>
       </c>
-      <c r="M79" s="30">
+      <c r="M79" s="28">
         <v>990</v>
       </c>
-      <c r="N79" s="30">
+      <c r="N79" s="28">
         <v>1508</v>
       </c>
-      <c r="O79" s="30">
+      <c r="O79" s="28">
         <v>5634</v>
       </c>
-      <c r="P79" s="27"/>
+      <c r="P79" s="25"/>
     </row>
     <row r="80" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I80" s="29" t="s">
+      <c r="I80" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="J80" s="30">
+      <c r="J80" s="28">
         <v>1598</v>
       </c>
-      <c r="K80" s="30">
+      <c r="K80" s="28">
         <v>1907</v>
       </c>
-      <c r="L80" s="30">
+      <c r="L80" s="28">
         <v>869</v>
       </c>
-      <c r="M80" s="30">
+      <c r="M80" s="28">
         <v>1426</v>
       </c>
-      <c r="N80" s="30">
+      <c r="N80" s="28">
         <v>1416</v>
       </c>
-      <c r="O80" s="30">
+      <c r="O80" s="28">
         <v>7216</v>
       </c>
-      <c r="P80" s="27"/>
+      <c r="P80" s="25"/>
     </row>
     <row r="81" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I81" s="29" t="s">
+      <c r="I81" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="J81" s="30">
+      <c r="J81" s="28">
         <v>900</v>
       </c>
-      <c r="K81" s="30">
+      <c r="K81" s="28">
         <v>1016</v>
       </c>
-      <c r="L81" s="30">
+      <c r="L81" s="28">
         <v>960</v>
       </c>
-      <c r="M81" s="30">
+      <c r="M81" s="28">
         <v>940</v>
       </c>
-      <c r="N81" s="30">
+      <c r="N81" s="28">
         <v>1193</v>
       </c>
-      <c r="O81" s="30">
+      <c r="O81" s="28">
         <v>5009</v>
       </c>
-      <c r="P81" s="27"/>
+      <c r="P81" s="25"/>
     </row>
     <row r="82" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I82" s="29" t="s">
+      <c r="I82" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="J82" s="30">
+      <c r="J82" s="28">
         <v>900</v>
       </c>
-      <c r="K82" s="30">
+      <c r="K82" s="28">
         <v>1470</v>
       </c>
-      <c r="L82" s="30">
+      <c r="L82" s="28">
         <v>1617</v>
       </c>
-      <c r="M82" s="30">
+      <c r="M82" s="28">
         <v>1314</v>
       </c>
-      <c r="N82" s="30">
+      <c r="N82" s="28">
         <v>941</v>
       </c>
-      <c r="O82" s="30">
+      <c r="O82" s="28">
         <v>6242</v>
       </c>
-      <c r="P82" s="27"/>
+      <c r="P82" s="25"/>
     </row>
     <row r="83" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I83" s="29" t="s">
+      <c r="I83" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="J83" s="30">
+      <c r="J83" s="28">
         <v>1255</v>
       </c>
-      <c r="K83" s="30">
+      <c r="K83" s="28">
         <v>516</v>
       </c>
-      <c r="L83" s="30">
+      <c r="L83" s="28">
         <v>1874</v>
       </c>
-      <c r="M83" s="30">
+      <c r="M83" s="28">
         <v>1863</v>
       </c>
-      <c r="N83" s="30">
+      <c r="N83" s="28">
         <v>1722</v>
       </c>
-      <c r="O83" s="30">
+      <c r="O83" s="28">
         <v>7230</v>
       </c>
-      <c r="P83" s="27"/>
+      <c r="P83" s="25"/>
     </row>
     <row r="84" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I84" s="29" t="s">
+      <c r="I84" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J84" s="30">
+      <c r="J84" s="28">
         <v>1138</v>
       </c>
-      <c r="K84" s="30">
+      <c r="K84" s="28">
         <v>1898</v>
       </c>
-      <c r="L84" s="30">
+      <c r="L84" s="28">
         <v>1482</v>
       </c>
-      <c r="M84" s="30">
+      <c r="M84" s="28">
         <v>846</v>
       </c>
-      <c r="N84" s="30">
+      <c r="N84" s="28">
         <v>1154</v>
       </c>
-      <c r="O84" s="30">
+      <c r="O84" s="28">
         <v>6518</v>
       </c>
-      <c r="P84" s="27"/>
+      <c r="P84" s="25"/>
     </row>
     <row r="85" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I85" s="28" t="s">
+      <c r="I85" s="26" t="s">
         <v>1000</v>
       </c>
-      <c r="J85" s="27"/>
-      <c r="K85" s="27"/>
-      <c r="L85" s="27"/>
-      <c r="M85" s="27"/>
-      <c r="N85" s="27"/>
-      <c r="O85" s="27"/>
-      <c r="P85" s="27"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="25"/>
+      <c r="L85" s="25"/>
+      <c r="M85" s="25"/>
+      <c r="N85" s="25"/>
+      <c r="O85" s="25"/>
+      <c r="P85" s="25"/>
     </row>
     <row r="86" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I86" s="29" t="s">
+      <c r="I86" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="J86" s="30">
+      <c r="J86" s="28">
         <v>1655</v>
       </c>
-      <c r="K86" s="30">
+      <c r="K86" s="28">
         <v>805</v>
       </c>
-      <c r="L86" s="30">
+      <c r="L86" s="28">
         <v>2263</v>
       </c>
-      <c r="M86" s="30">
+      <c r="M86" s="28">
         <v>987</v>
       </c>
-      <c r="N86" s="30">
+      <c r="N86" s="28">
         <v>1075</v>
       </c>
-      <c r="O86" s="30">
+      <c r="O86" s="28">
         <v>6785</v>
       </c>
-      <c r="P86" s="27"/>
+      <c r="P86" s="25"/>
     </row>
     <row r="87" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I87" s="29" t="s">
+      <c r="I87" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="J87" s="30">
+      <c r="J87" s="28">
         <v>1104</v>
       </c>
-      <c r="K87" s="30">
+      <c r="K87" s="28">
         <v>2280</v>
       </c>
-      <c r="L87" s="30">
+      <c r="L87" s="28">
         <v>1445</v>
       </c>
-      <c r="M87" s="30">
+      <c r="M87" s="28">
         <v>1722</v>
       </c>
-      <c r="N87" s="30">
+      <c r="N87" s="28">
         <v>1196</v>
       </c>
-      <c r="O87" s="30">
+      <c r="O87" s="28">
         <v>7747</v>
       </c>
-      <c r="P87" s="27"/>
+      <c r="P87" s="25"/>
     </row>
     <row r="88" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I88" s="29" t="s">
+      <c r="I88" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="J88" s="30">
+      <c r="J88" s="28">
         <v>372</v>
       </c>
-      <c r="K88" s="30">
+      <c r="K88" s="28">
         <v>1818</v>
       </c>
-      <c r="L88" s="30">
+      <c r="L88" s="28">
         <v>1346</v>
       </c>
-      <c r="M88" s="30">
+      <c r="M88" s="28">
         <v>1156</v>
       </c>
-      <c r="N88" s="30">
+      <c r="N88" s="28">
         <v>1484</v>
       </c>
-      <c r="O88" s="30">
+      <c r="O88" s="28">
         <v>6176</v>
       </c>
-      <c r="P88" s="27"/>
+      <c r="P88" s="25"/>
     </row>
     <row r="89" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I89" s="29" t="s">
+      <c r="I89" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="J89" s="30">
+      <c r="J89" s="28">
         <v>1415</v>
       </c>
-      <c r="K89" s="30">
+      <c r="K89" s="28">
         <v>1271</v>
       </c>
-      <c r="L89" s="30">
+      <c r="L89" s="28">
         <v>1214</v>
       </c>
-      <c r="M89" s="30">
+      <c r="M89" s="28">
         <v>1135</v>
       </c>
-      <c r="N89" s="30">
+      <c r="N89" s="28">
         <v>1566</v>
       </c>
-      <c r="O89" s="30">
+      <c r="O89" s="28">
         <v>6601</v>
       </c>
-      <c r="P89" s="27"/>
+      <c r="P89" s="25"/>
     </row>
     <row r="90" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="I90" s="29" t="s">
+      <c r="I90" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="J90" s="30">
+      <c r="J90" s="28">
         <v>1362</v>
       </c>
-      <c r="K90" s="30">
+      <c r="K90" s="28">
         <v>1363</v>
       </c>
-      <c r="L90" s="30">
+      <c r="L90" s="28">
         <v>1152</v>
       </c>
-      <c r="M90" s="30">
+      <c r="M90" s="28">
         <v>777</v>
       </c>
-      <c r="N90" s="30">
+      <c r="N90" s="28">
         <v>750</v>
       </c>
-      <c r="O90" s="30">
+      <c r="O90" s="28">
         <v>5404</v>
       </c>
-      <c r="P90" s="27"/>
+      <c r="P90" s="25"/>
     </row>
     <row r="91" spans="9:16" x14ac:dyDescent="0.35">
-      <c r="P91" s="27"/>
+      <c r="P91" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -57033,4294 +57011,491 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413AC5A4-4AEB-49E6-838D-C00B19AAAE9E}">
-  <dimension ref="A1:AV80"/>
+  <dimension ref="D1:AE38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.90625" customWidth="1"/>
-    <col min="2" max="2" width="3" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" customWidth="1"/>
-    <col min="25" max="25" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.90625" style="32" customWidth="1"/>
+    <col min="2" max="2" width="3" style="32" customWidth="1"/>
+    <col min="3" max="5" width="8.7265625" style="32"/>
+    <col min="6" max="6" width="4.54296875" style="32" customWidth="1"/>
+    <col min="7" max="24" width="8.7265625" style="32"/>
+    <col min="25" max="25" width="9.7265625" style="32" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="8.7265625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="49" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="22"/>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="46" t="s">
+    <row r="1" spans="4:8" ht="49" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D1" s="30" t="s">
         <v>1081</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="22"/>
-      <c r="AM1" s="22"/>
-      <c r="AN1" s="22"/>
-      <c r="AO1" s="22"/>
-      <c r="AP1" s="22"/>
-      <c r="AQ1" s="22"/>
-      <c r="AR1" s="22"/>
-      <c r="AS1" s="22"/>
-      <c r="AT1" s="22"/>
-      <c r="AU1" s="22"/>
-      <c r="AV1" s="22"/>
-    </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22"/>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="22"/>
-      <c r="AK2" s="22"/>
-      <c r="AL2" s="22"/>
-      <c r="AM2" s="22"/>
-      <c r="AN2" s="22"/>
-      <c r="AO2" s="22"/>
-      <c r="AP2" s="22"/>
-      <c r="AQ2" s="22"/>
-      <c r="AR2" s="22"/>
-      <c r="AS2" s="22"/>
-      <c r="AT2" s="22"/>
-      <c r="AU2" s="22"/>
-      <c r="AV2" s="22"/>
-    </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="22"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="22"/>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="22"/>
-      <c r="AM3" s="22"/>
-      <c r="AN3" s="22"/>
-      <c r="AO3" s="22"/>
-      <c r="AP3" s="22"/>
-      <c r="AQ3" s="22"/>
-      <c r="AR3" s="22"/>
-      <c r="AS3" s="22"/>
-      <c r="AT3" s="22"/>
-      <c r="AU3" s="22"/>
-      <c r="AV3" s="22"/>
-    </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="22"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="22"/>
-      <c r="AB4" s="22"/>
-      <c r="AC4" s="22"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="22"/>
-      <c r="AF4" s="22"/>
-      <c r="AG4" s="22"/>
-      <c r="AH4" s="22"/>
-      <c r="AI4" s="22"/>
-      <c r="AJ4" s="22"/>
-      <c r="AK4" s="22"/>
-      <c r="AL4" s="22"/>
-      <c r="AM4" s="22"/>
-      <c r="AN4" s="22"/>
-      <c r="AO4" s="22"/>
-      <c r="AP4" s="22"/>
-      <c r="AQ4" s="22"/>
-      <c r="AR4" s="22"/>
-      <c r="AS4" s="22"/>
-      <c r="AT4" s="22"/>
-      <c r="AU4" s="22"/>
-      <c r="AV4" s="22"/>
-    </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="22"/>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="22"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="22"/>
-      <c r="AH5" s="22"/>
-      <c r="AI5" s="22"/>
-      <c r="AJ5" s="22"/>
-      <c r="AK5" s="22"/>
-      <c r="AL5" s="22"/>
-      <c r="AM5" s="22"/>
-      <c r="AN5" s="22"/>
-      <c r="AO5" s="22"/>
-      <c r="AP5" s="22"/>
-      <c r="AQ5" s="22"/>
-      <c r="AR5" s="22"/>
-      <c r="AS5" s="22"/>
-      <c r="AT5" s="22"/>
-      <c r="AU5" s="22"/>
-      <c r="AV5" s="22"/>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="22"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="22"/>
-      <c r="AH6" s="22"/>
-      <c r="AI6" s="22"/>
-      <c r="AJ6" s="22"/>
-      <c r="AK6" s="22"/>
-      <c r="AL6" s="22"/>
-      <c r="AM6" s="22"/>
-      <c r="AN6" s="22"/>
-      <c r="AO6" s="22"/>
-      <c r="AP6" s="22"/>
-      <c r="AQ6" s="22"/>
-      <c r="AR6" s="22"/>
-      <c r="AS6" s="22"/>
-      <c r="AT6" s="22"/>
-      <c r="AU6" s="22"/>
-      <c r="AV6" s="22"/>
-    </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-      <c r="AD7" s="22"/>
-      <c r="AE7" s="22"/>
-      <c r="AF7" s="22"/>
-      <c r="AG7" s="22"/>
-      <c r="AH7" s="22"/>
-      <c r="AI7" s="22"/>
-      <c r="AJ7" s="22"/>
-      <c r="AK7" s="22"/>
-      <c r="AL7" s="22"/>
-      <c r="AM7" s="22"/>
-      <c r="AN7" s="22"/>
-      <c r="AO7" s="22"/>
-      <c r="AP7" s="22"/>
-      <c r="AQ7" s="22"/>
-      <c r="AR7" s="22"/>
-      <c r="AS7" s="22"/>
-      <c r="AT7" s="22"/>
-      <c r="AU7" s="22"/>
-      <c r="AV7" s="22"/>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22"/>
-      <c r="AD8" s="22"/>
-      <c r="AE8" s="22"/>
-      <c r="AF8" s="22"/>
-      <c r="AG8" s="22"/>
-      <c r="AH8" s="22"/>
-      <c r="AI8" s="22"/>
-      <c r="AJ8" s="22"/>
-      <c r="AK8" s="22"/>
-      <c r="AL8" s="22"/>
-      <c r="AM8" s="22"/>
-      <c r="AN8" s="22"/>
-      <c r="AO8" s="22"/>
-      <c r="AP8" s="22"/>
-      <c r="AQ8" s="22"/>
-      <c r="AR8" s="22"/>
-      <c r="AS8" s="22"/>
-      <c r="AT8" s="22"/>
-      <c r="AU8" s="22"/>
-      <c r="AV8" s="22"/>
-    </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-      <c r="AD9" s="22"/>
-      <c r="AE9" s="22"/>
-      <c r="AF9" s="22"/>
-      <c r="AG9" s="22"/>
-      <c r="AH9" s="22"/>
-      <c r="AI9" s="22"/>
-      <c r="AJ9" s="22"/>
-      <c r="AK9" s="22"/>
-      <c r="AL9" s="22"/>
-      <c r="AM9" s="22"/>
-      <c r="AN9" s="22"/>
-      <c r="AO9" s="22"/>
-      <c r="AP9" s="22"/>
-      <c r="AQ9" s="22"/>
-      <c r="AR9" s="22"/>
-      <c r="AS9" s="22"/>
-      <c r="AT9" s="22"/>
-      <c r="AU9" s="22"/>
-      <c r="AV9" s="22"/>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="22"/>
-      <c r="AD10" s="22"/>
-      <c r="AE10" s="22"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="22"/>
-      <c r="AH10" s="22"/>
-      <c r="AI10" s="22"/>
-      <c r="AJ10" s="22"/>
-      <c r="AK10" s="22"/>
-      <c r="AL10" s="22"/>
-      <c r="AM10" s="22"/>
-      <c r="AN10" s="22"/>
-      <c r="AO10" s="22"/>
-      <c r="AP10" s="22"/>
-      <c r="AQ10" s="22"/>
-      <c r="AR10" s="22"/>
-      <c r="AS10" s="22"/>
-      <c r="AT10" s="22"/>
-      <c r="AU10" s="22"/>
-      <c r="AV10" s="22"/>
-    </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="22"/>
-      <c r="AH11" s="22"/>
-      <c r="AI11" s="22"/>
-      <c r="AJ11" s="22"/>
-      <c r="AK11" s="22"/>
-      <c r="AL11" s="22"/>
-      <c r="AM11" s="22"/>
-      <c r="AN11" s="22"/>
-      <c r="AO11" s="22"/>
-      <c r="AP11" s="22"/>
-      <c r="AQ11" s="22"/>
-      <c r="AR11" s="22"/>
-      <c r="AS11" s="22"/>
-      <c r="AT11" s="22"/>
-      <c r="AU11" s="22"/>
-      <c r="AV11" s="22"/>
-    </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="22"/>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="22"/>
-      <c r="AF12" s="22"/>
-      <c r="AG12" s="22"/>
-      <c r="AH12" s="22"/>
-      <c r="AI12" s="22"/>
-      <c r="AJ12" s="22"/>
-      <c r="AK12" s="22"/>
-      <c r="AL12" s="22"/>
-      <c r="AM12" s="22"/>
-      <c r="AN12" s="22"/>
-      <c r="AO12" s="22"/>
-      <c r="AP12" s="22"/>
-      <c r="AQ12" s="22"/>
-      <c r="AR12" s="22"/>
-      <c r="AS12" s="22"/>
-      <c r="AT12" s="22"/>
-      <c r="AU12" s="22"/>
-      <c r="AV12" s="22"/>
-    </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22"/>
-      <c r="AH13" s="22"/>
-      <c r="AI13" s="22"/>
-      <c r="AJ13" s="22"/>
-      <c r="AK13" s="22"/>
-      <c r="AL13" s="22"/>
-      <c r="AM13" s="22"/>
-      <c r="AN13" s="22"/>
-      <c r="AO13" s="22"/>
-      <c r="AP13" s="22"/>
-      <c r="AQ13" s="22"/>
-      <c r="AR13" s="22"/>
-      <c r="AS13" s="22"/>
-      <c r="AT13" s="22"/>
-      <c r="AU13" s="22"/>
-      <c r="AV13" s="22"/>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="22"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="22"/>
-      <c r="AH14" s="22"/>
-      <c r="AI14" s="22"/>
-      <c r="AJ14" s="22"/>
-      <c r="AK14" s="22"/>
-      <c r="AL14" s="22"/>
-      <c r="AM14" s="22"/>
-      <c r="AN14" s="22"/>
-      <c r="AO14" s="22"/>
-      <c r="AP14" s="22"/>
-      <c r="AQ14" s="22"/>
-      <c r="AR14" s="22"/>
-      <c r="AS14" s="22"/>
-      <c r="AT14" s="22"/>
-      <c r="AU14" s="22"/>
-      <c r="AV14" s="22"/>
-    </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="22"/>
-      <c r="AC15" s="22"/>
-      <c r="AD15" s="22"/>
-      <c r="AE15" s="22"/>
-      <c r="AF15" s="22"/>
-      <c r="AG15" s="22"/>
-      <c r="AH15" s="22"/>
-      <c r="AI15" s="22"/>
-      <c r="AJ15" s="22"/>
-      <c r="AK15" s="22"/>
-      <c r="AL15" s="22"/>
-      <c r="AM15" s="22"/>
-      <c r="AN15" s="22"/>
-      <c r="AO15" s="22"/>
-      <c r="AP15" s="22"/>
-      <c r="AQ15" s="22"/>
-      <c r="AR15" s="22"/>
-      <c r="AS15" s="22"/>
-      <c r="AT15" s="22"/>
-      <c r="AU15" s="22"/>
-      <c r="AV15" s="22"/>
-    </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="22"/>
-      <c r="AC16" s="22"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="22"/>
-      <c r="AF16" s="22"/>
-      <c r="AG16" s="22"/>
-      <c r="AH16" s="22"/>
-      <c r="AI16" s="22"/>
-      <c r="AJ16" s="22"/>
-      <c r="AK16" s="22"/>
-      <c r="AL16" s="22"/>
-      <c r="AM16" s="22"/>
-      <c r="AN16" s="22"/>
-      <c r="AO16" s="22"/>
-      <c r="AP16" s="22"/>
-      <c r="AQ16" s="22"/>
-      <c r="AR16" s="22"/>
-      <c r="AS16" s="22"/>
-      <c r="AT16" s="22"/>
-      <c r="AU16" s="22"/>
-      <c r="AV16" s="22"/>
-    </row>
-    <row r="17" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="22"/>
-      <c r="AC17" s="22"/>
-      <c r="AD17" s="22"/>
-      <c r="AE17" s="22"/>
-      <c r="AF17" s="22"/>
-      <c r="AG17" s="22"/>
-      <c r="AH17" s="22"/>
-      <c r="AI17" s="22"/>
-      <c r="AJ17" s="22"/>
-      <c r="AK17" s="22"/>
-      <c r="AL17" s="22"/>
-      <c r="AM17" s="22"/>
-      <c r="AN17" s="22"/>
-      <c r="AO17" s="22"/>
-      <c r="AP17" s="22"/>
-      <c r="AQ17" s="22"/>
-      <c r="AR17" s="22"/>
-      <c r="AS17" s="22"/>
-      <c r="AT17" s="22"/>
-      <c r="AU17" s="22"/>
-      <c r="AV17" s="22"/>
-    </row>
-    <row r="18" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="22"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="22"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="22"/>
-      <c r="AC18" s="22"/>
-      <c r="AD18" s="22"/>
-      <c r="AE18" s="22"/>
-      <c r="AF18" s="22"/>
-      <c r="AG18" s="22"/>
-      <c r="AH18" s="22"/>
-      <c r="AI18" s="22"/>
-      <c r="AJ18" s="22"/>
-      <c r="AK18" s="22"/>
-      <c r="AL18" s="22"/>
-      <c r="AM18" s="22"/>
-      <c r="AN18" s="22"/>
-      <c r="AO18" s="22"/>
-      <c r="AP18" s="22"/>
-      <c r="AQ18" s="22"/>
-      <c r="AR18" s="22"/>
-      <c r="AS18" s="22"/>
-      <c r="AT18" s="22"/>
-      <c r="AU18" s="22"/>
-      <c r="AV18" s="22"/>
-    </row>
-    <row r="19" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="22"/>
-      <c r="Q19" s="22"/>
-      <c r="R19" s="22"/>
-      <c r="S19" s="22"/>
-      <c r="T19" s="22"/>
-      <c r="U19" s="22"/>
-      <c r="V19" s="22"/>
-      <c r="W19" s="22"/>
-      <c r="X19" s="22"/>
-      <c r="Y19" s="22"/>
-      <c r="Z19" s="22"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="22"/>
-      <c r="AC19" s="22"/>
-      <c r="AD19" s="22"/>
-      <c r="AE19" s="22"/>
-      <c r="AF19" s="22"/>
-      <c r="AG19" s="22"/>
-      <c r="AH19" s="22"/>
-      <c r="AI19" s="22"/>
-      <c r="AJ19" s="22"/>
-      <c r="AK19" s="22"/>
-      <c r="AL19" s="22"/>
-      <c r="AM19" s="22"/>
-      <c r="AN19" s="22"/>
-      <c r="AO19" s="22"/>
-      <c r="AP19" s="22"/>
-      <c r="AQ19" s="22"/>
-      <c r="AR19" s="22"/>
-      <c r="AS19" s="22"/>
-      <c r="AT19" s="22"/>
-      <c r="AU19" s="22"/>
-      <c r="AV19" s="22"/>
-    </row>
-    <row r="20" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="22"/>
-      <c r="W20" s="22"/>
-      <c r="X20" s="22"/>
-      <c r="Y20" s="33"/>
-      <c r="Z20" s="39" t="str" cm="1">
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+    </row>
+    <row r="5" spans="4:8" x14ac:dyDescent="0.35">
+      <c r="F5" s="33"/>
+    </row>
+    <row r="20" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y20" s="36"/>
+      <c r="Z20" s="37" t="str" cm="1">
         <f t="array" ref="Z20:AD20">'Pivots '!J72:N72</f>
         <v>R01</v>
       </c>
-      <c r="AA20" s="39" t="str">
+      <c r="AA20" s="37" t="str">
         <v>R02</v>
       </c>
-      <c r="AB20" s="39" t="str">
+      <c r="AB20" s="37" t="str">
         <v>R03</v>
       </c>
-      <c r="AC20" s="39" t="str">
+      <c r="AC20" s="37" t="str">
         <v>R04</v>
       </c>
-      <c r="AD20" s="39" t="str">
+      <c r="AD20" s="37" t="str">
         <v>R05</v>
       </c>
-      <c r="AE20" s="40" t="s">
+      <c r="AE20" s="38" t="s">
         <v>1074</v>
       </c>
-      <c r="AF20" s="22"/>
-      <c r="AG20" s="22"/>
-      <c r="AH20" s="22"/>
-      <c r="AI20" s="22"/>
-      <c r="AJ20" s="22"/>
-      <c r="AK20" s="22"/>
-      <c r="AL20" s="22"/>
-      <c r="AM20" s="22"/>
-      <c r="AN20" s="22"/>
-      <c r="AO20" s="22"/>
-      <c r="AP20" s="22"/>
-      <c r="AQ20" s="22"/>
-      <c r="AR20" s="22"/>
-      <c r="AS20" s="22"/>
-      <c r="AT20" s="22"/>
-      <c r="AU20" s="22"/>
-      <c r="AV20" s="22"/>
-    </row>
-    <row r="21" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="22"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="22"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="22"/>
-      <c r="X21" s="22"/>
-      <c r="Y21" s="42" t="str" cm="1">
+    </row>
+    <row r="21" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y21" s="39" t="str" cm="1">
         <f t="array" ref="Y21:AE38">IF('Pivots '!I73:O90="","",'Pivots '!I73:O90)</f>
         <v>Cincinnati</v>
       </c>
-      <c r="Z21" s="31" t="str">
+      <c r="Z21" s="40" t="str">
         <v/>
       </c>
-      <c r="AA21" s="31" t="str">
+      <c r="AA21" s="40" t="str">
         <v/>
       </c>
-      <c r="AB21" s="31" t="str">
+      <c r="AB21" s="40" t="str">
         <v/>
       </c>
-      <c r="AC21" s="31" t="str">
+      <c r="AC21" s="40" t="str">
         <v/>
       </c>
-      <c r="AD21" s="31" t="str">
+      <c r="AD21" s="40" t="str">
         <v/>
       </c>
       <c r="AE21" s="41" t="str">
         <v/>
       </c>
-      <c r="AF21" s="22"/>
-      <c r="AG21" s="22"/>
-      <c r="AH21" s="22"/>
-      <c r="AI21" s="22"/>
-      <c r="AJ21" s="22"/>
-      <c r="AK21" s="22"/>
-      <c r="AL21" s="22"/>
-      <c r="AM21" s="22"/>
-      <c r="AN21" s="22"/>
-      <c r="AO21" s="22"/>
-      <c r="AP21" s="22"/>
-      <c r="AQ21" s="22"/>
-      <c r="AR21" s="22"/>
-      <c r="AS21" s="22"/>
-      <c r="AT21" s="22"/>
-      <c r="AU21" s="22"/>
-      <c r="AV21" s="22"/>
-    </row>
-    <row r="22" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="22"/>
-      <c r="X22" s="22"/>
-      <c r="Y22" s="34" t="str">
+    </row>
+    <row r="22" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y22" s="39" t="str">
         <v>C0003</v>
       </c>
-      <c r="Z22" s="32">
+      <c r="Z22" s="42">
         <v>891</v>
       </c>
-      <c r="AA22" s="32">
+      <c r="AA22" s="42">
         <v>1332</v>
       </c>
-      <c r="AB22" s="32">
+      <c r="AB22" s="42">
         <v>1282</v>
       </c>
-      <c r="AC22" s="32">
+      <c r="AC22" s="42">
         <v>739</v>
       </c>
-      <c r="AD22" s="32">
+      <c r="AD22" s="42">
         <v>560</v>
       </c>
-      <c r="AE22" s="35">
+      <c r="AE22" s="43">
         <v>4804</v>
       </c>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="22"/>
-      <c r="AI22" s="22"/>
-      <c r="AJ22" s="22"/>
-      <c r="AK22" s="22"/>
-      <c r="AL22" s="22"/>
-      <c r="AM22" s="22"/>
-      <c r="AN22" s="22"/>
-      <c r="AO22" s="22"/>
-      <c r="AP22" s="22"/>
-      <c r="AQ22" s="22"/>
-      <c r="AR22" s="22"/>
-      <c r="AS22" s="22"/>
-      <c r="AT22" s="22"/>
-      <c r="AU22" s="22"/>
-      <c r="AV22" s="22"/>
-    </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="22"/>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="34" t="str">
+    </row>
+    <row r="23" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y23" s="39" t="str">
         <v>C0004</v>
       </c>
-      <c r="Z23" s="32">
+      <c r="Z23" s="42">
         <v>1991</v>
       </c>
-      <c r="AA23" s="32">
+      <c r="AA23" s="42">
         <v>1886</v>
       </c>
-      <c r="AB23" s="32">
+      <c r="AB23" s="42">
         <v>1206</v>
       </c>
-      <c r="AC23" s="32">
+      <c r="AC23" s="42">
         <v>884</v>
       </c>
-      <c r="AD23" s="32">
+      <c r="AD23" s="42">
         <v>1722</v>
       </c>
-      <c r="AE23" s="35">
+      <c r="AE23" s="43">
         <v>7689</v>
       </c>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="22"/>
-      <c r="AI23" s="22"/>
-      <c r="AJ23" s="22"/>
-      <c r="AK23" s="22"/>
-      <c r="AL23" s="22"/>
-      <c r="AM23" s="22"/>
-      <c r="AN23" s="22"/>
-      <c r="AO23" s="22"/>
-      <c r="AP23" s="22"/>
-      <c r="AQ23" s="22"/>
-      <c r="AR23" s="22"/>
-      <c r="AS23" s="22"/>
-      <c r="AT23" s="22"/>
-      <c r="AU23" s="22"/>
-      <c r="AV23" s="22"/>
-    </row>
-    <row r="24" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="22"/>
-      <c r="S24" s="22"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="22"/>
-      <c r="X24" s="22"/>
-      <c r="Y24" s="34" t="str">
+    </row>
+    <row r="24" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y24" s="39" t="str">
         <v>C0011</v>
       </c>
-      <c r="Z24" s="32">
+      <c r="Z24" s="42">
         <v>1163</v>
       </c>
-      <c r="AA24" s="32">
+      <c r="AA24" s="42">
         <v>1180</v>
       </c>
-      <c r="AB24" s="32">
+      <c r="AB24" s="42">
         <v>1616</v>
       </c>
-      <c r="AC24" s="32">
+      <c r="AC24" s="42">
         <v>1043</v>
       </c>
-      <c r="AD24" s="32">
+      <c r="AD24" s="42">
         <v>1747</v>
       </c>
-      <c r="AE24" s="35">
+      <c r="AE24" s="43">
         <v>6749</v>
       </c>
-      <c r="AF24" s="22"/>
-      <c r="AG24" s="22"/>
-      <c r="AH24" s="22"/>
-      <c r="AI24" s="22"/>
-      <c r="AJ24" s="22"/>
-      <c r="AK24" s="22"/>
-      <c r="AL24" s="22"/>
-      <c r="AM24" s="22"/>
-      <c r="AN24" s="22"/>
-      <c r="AO24" s="22"/>
-      <c r="AP24" s="22"/>
-      <c r="AQ24" s="22"/>
-      <c r="AR24" s="22"/>
-      <c r="AS24" s="22"/>
-      <c r="AT24" s="22"/>
-      <c r="AU24" s="22"/>
-      <c r="AV24" s="22"/>
-    </row>
-    <row r="25" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="22"/>
-      <c r="X25" s="22"/>
-      <c r="Y25" s="34" t="str">
+    </row>
+    <row r="25" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y25" s="39" t="str">
         <v>C0012</v>
       </c>
-      <c r="Z25" s="32">
+      <c r="Z25" s="42">
         <v>1438</v>
       </c>
-      <c r="AA25" s="32">
+      <c r="AA25" s="42">
         <v>1616</v>
       </c>
-      <c r="AB25" s="32">
+      <c r="AB25" s="42">
         <v>866</v>
       </c>
-      <c r="AC25" s="32">
+      <c r="AC25" s="42">
         <v>829</v>
       </c>
-      <c r="AD25" s="32">
+      <c r="AD25" s="42">
         <v>2070</v>
       </c>
-      <c r="AE25" s="35">
+      <c r="AE25" s="43">
         <v>6819</v>
       </c>
-      <c r="AF25" s="22"/>
-      <c r="AG25" s="22"/>
-      <c r="AH25" s="22"/>
-      <c r="AI25" s="22"/>
-      <c r="AJ25" s="22"/>
-      <c r="AK25" s="22"/>
-      <c r="AL25" s="22"/>
-      <c r="AM25" s="22"/>
-      <c r="AN25" s="22"/>
-      <c r="AO25" s="22"/>
-      <c r="AP25" s="22"/>
-      <c r="AQ25" s="22"/>
-      <c r="AR25" s="22"/>
-      <c r="AS25" s="22"/>
-      <c r="AT25" s="22"/>
-      <c r="AU25" s="22"/>
-      <c r="AV25" s="22"/>
-    </row>
-    <row r="26" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="22"/>
-      <c r="T26" s="22"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="22"/>
-      <c r="X26" s="22"/>
-      <c r="Y26" s="42" t="str">
+    </row>
+    <row r="26" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y26" s="39" t="str">
         <v>Cleveland</v>
       </c>
-      <c r="Z26" s="32" t="str">
+      <c r="Z26" s="42" t="str">
         <v/>
       </c>
-      <c r="AA26" s="32" t="str">
+      <c r="AA26" s="42" t="str">
         <v/>
       </c>
-      <c r="AB26" s="32" t="str">
+      <c r="AB26" s="42" t="str">
         <v/>
       </c>
-      <c r="AC26" s="32" t="str">
+      <c r="AC26" s="42" t="str">
         <v/>
       </c>
-      <c r="AD26" s="32" t="str">
+      <c r="AD26" s="42" t="str">
         <v/>
       </c>
-      <c r="AE26" s="35" t="str">
+      <c r="AE26" s="43" t="str">
         <v/>
       </c>
-      <c r="AF26" s="22"/>
-      <c r="AG26" s="22"/>
-      <c r="AH26" s="22"/>
-      <c r="AI26" s="22"/>
-      <c r="AJ26" s="22"/>
-      <c r="AK26" s="22"/>
-      <c r="AL26" s="22"/>
-      <c r="AM26" s="22"/>
-      <c r="AN26" s="22"/>
-      <c r="AO26" s="22"/>
-      <c r="AP26" s="22"/>
-      <c r="AQ26" s="22"/>
-      <c r="AR26" s="22"/>
-      <c r="AS26" s="22"/>
-      <c r="AT26" s="22"/>
-      <c r="AU26" s="22"/>
-      <c r="AV26" s="22"/>
-    </row>
-    <row r="27" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="22"/>
-      <c r="X27" s="22"/>
-      <c r="Y27" s="34" t="str">
+    </row>
+    <row r="27" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y27" s="39" t="str">
         <v>C0002</v>
       </c>
-      <c r="Z27" s="32">
+      <c r="Z27" s="42">
         <v>1233</v>
       </c>
-      <c r="AA27" s="32">
+      <c r="AA27" s="42">
         <v>223</v>
       </c>
-      <c r="AB27" s="32">
+      <c r="AB27" s="42">
         <v>1680</v>
       </c>
-      <c r="AC27" s="32">
+      <c r="AC27" s="42">
         <v>990</v>
       </c>
-      <c r="AD27" s="32">
+      <c r="AD27" s="42">
         <v>1508</v>
       </c>
-      <c r="AE27" s="35">
+      <c r="AE27" s="43">
         <v>5634</v>
       </c>
-      <c r="AF27" s="22"/>
-      <c r="AG27" s="22"/>
-      <c r="AH27" s="22"/>
-      <c r="AI27" s="22"/>
-      <c r="AJ27" s="22"/>
-      <c r="AK27" s="22"/>
-      <c r="AL27" s="22"/>
-      <c r="AM27" s="22"/>
-      <c r="AN27" s="22"/>
-      <c r="AO27" s="22"/>
-      <c r="AP27" s="22"/>
-      <c r="AQ27" s="22"/>
-      <c r="AR27" s="22"/>
-      <c r="AS27" s="22"/>
-      <c r="AT27" s="22"/>
-      <c r="AU27" s="22"/>
-      <c r="AV27" s="22"/>
-    </row>
-    <row r="28" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="34" t="str">
+    </row>
+    <row r="28" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y28" s="39" t="str">
         <v>C0007</v>
       </c>
-      <c r="Z28" s="32">
+      <c r="Z28" s="42">
         <v>1598</v>
       </c>
-      <c r="AA28" s="32">
+      <c r="AA28" s="42">
         <v>1907</v>
       </c>
-      <c r="AB28" s="32">
+      <c r="AB28" s="42">
         <v>869</v>
       </c>
-      <c r="AC28" s="32">
+      <c r="AC28" s="42">
         <v>1426</v>
       </c>
-      <c r="AD28" s="32">
+      <c r="AD28" s="42">
         <v>1416</v>
       </c>
-      <c r="AE28" s="35">
+      <c r="AE28" s="43">
         <v>7216</v>
       </c>
-      <c r="AF28" s="22"/>
-      <c r="AG28" s="22"/>
-      <c r="AH28" s="22"/>
-      <c r="AI28" s="22"/>
-      <c r="AJ28" s="22"/>
-      <c r="AK28" s="22"/>
-      <c r="AL28" s="22"/>
-      <c r="AM28" s="22"/>
-      <c r="AN28" s="22"/>
-      <c r="AO28" s="22"/>
-      <c r="AP28" s="22"/>
-      <c r="AQ28" s="22"/>
-      <c r="AR28" s="22"/>
-      <c r="AS28" s="22"/>
-      <c r="AT28" s="22"/>
-      <c r="AU28" s="22"/>
-      <c r="AV28" s="22"/>
-    </row>
-    <row r="29" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="22"/>
-      <c r="R29" s="22"/>
-      <c r="S29" s="22"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="22"/>
-      <c r="X29" s="22"/>
-      <c r="Y29" s="34" t="str">
+    </row>
+    <row r="29" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y29" s="39" t="str">
         <v>C0008</v>
       </c>
-      <c r="Z29" s="32">
+      <c r="Z29" s="42">
         <v>900</v>
       </c>
-      <c r="AA29" s="32">
+      <c r="AA29" s="42">
         <v>1016</v>
       </c>
-      <c r="AB29" s="32">
+      <c r="AB29" s="42">
         <v>960</v>
       </c>
-      <c r="AC29" s="32">
+      <c r="AC29" s="42">
         <v>940</v>
       </c>
-      <c r="AD29" s="32">
+      <c r="AD29" s="42">
         <v>1193</v>
       </c>
-      <c r="AE29" s="35">
+      <c r="AE29" s="43">
         <v>5009</v>
       </c>
-      <c r="AF29" s="22"/>
-      <c r="AG29" s="22"/>
-      <c r="AH29" s="22"/>
-      <c r="AI29" s="22"/>
-      <c r="AJ29" s="22"/>
-      <c r="AK29" s="22"/>
-      <c r="AL29" s="22"/>
-      <c r="AM29" s="22"/>
-      <c r="AN29" s="22"/>
-      <c r="AO29" s="22"/>
-      <c r="AP29" s="22"/>
-      <c r="AQ29" s="22"/>
-      <c r="AR29" s="22"/>
-      <c r="AS29" s="22"/>
-      <c r="AT29" s="22"/>
-      <c r="AU29" s="22"/>
-      <c r="AV29" s="22"/>
-    </row>
-    <row r="30" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="22"/>
-      <c r="R30" s="22"/>
-      <c r="S30" s="22"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="22"/>
-      <c r="X30" s="22"/>
-      <c r="Y30" s="34" t="str">
+    </row>
+    <row r="30" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="Y30" s="39" t="str">
         <v>C0010</v>
       </c>
-      <c r="Z30" s="32">
+      <c r="Z30" s="42">
         <v>900</v>
       </c>
-      <c r="AA30" s="32">
+      <c r="AA30" s="42">
         <v>1470</v>
       </c>
-      <c r="AB30" s="32">
+      <c r="AB30" s="42">
         <v>1617</v>
       </c>
-      <c r="AC30" s="32">
+      <c r="AC30" s="42">
         <v>1314</v>
       </c>
-      <c r="AD30" s="32">
+      <c r="AD30" s="42">
         <v>941</v>
       </c>
-      <c r="AE30" s="35">
+      <c r="AE30" s="43">
         <v>6242</v>
       </c>
-      <c r="AF30" s="22"/>
-      <c r="AG30" s="22"/>
-      <c r="AH30" s="22"/>
-      <c r="AI30" s="22"/>
-      <c r="AJ30" s="22"/>
-      <c r="AK30" s="22"/>
-      <c r="AL30" s="22"/>
-      <c r="AM30" s="22"/>
-      <c r="AN30" s="22"/>
-      <c r="AO30" s="22"/>
-      <c r="AP30" s="22"/>
-      <c r="AQ30" s="22"/>
-      <c r="AR30" s="22"/>
-      <c r="AS30" s="22"/>
-      <c r="AT30" s="22"/>
-      <c r="AU30" s="22"/>
-      <c r="AV30" s="22"/>
-    </row>
-    <row r="31" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="22"/>
-      <c r="R31" s="22"/>
-      <c r="S31" s="22"/>
-      <c r="T31" s="22"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="22"/>
-      <c r="W31" s="47" t="e" vm="6">
+    </row>
+    <row r="31" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="W31" s="34" t="e" vm="6">
         <f>'Pivots '!P66</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X31" s="22"/>
-      <c r="Y31" s="34" t="str">
+      <c r="Y31" s="39" t="str">
         <v>C0013</v>
       </c>
-      <c r="Z31" s="32">
+      <c r="Z31" s="42">
         <v>1255</v>
       </c>
-      <c r="AA31" s="32">
+      <c r="AA31" s="42">
         <v>516</v>
       </c>
-      <c r="AB31" s="32">
+      <c r="AB31" s="42">
         <v>1874</v>
       </c>
-      <c r="AC31" s="32">
+      <c r="AC31" s="42">
         <v>1863</v>
       </c>
-      <c r="AD31" s="32">
+      <c r="AD31" s="42">
         <v>1722</v>
       </c>
-      <c r="AE31" s="35">
+      <c r="AE31" s="43">
         <v>7230</v>
       </c>
-      <c r="AF31" s="22"/>
-      <c r="AG31" s="22"/>
-      <c r="AH31" s="22"/>
-      <c r="AI31" s="22"/>
-      <c r="AJ31" s="22"/>
-      <c r="AK31" s="22"/>
-      <c r="AL31" s="22"/>
-      <c r="AM31" s="22"/>
-      <c r="AN31" s="22"/>
-      <c r="AO31" s="22"/>
-      <c r="AP31" s="22"/>
-      <c r="AQ31" s="22"/>
-      <c r="AR31" s="22"/>
-      <c r="AS31" s="22"/>
-      <c r="AT31" s="22"/>
-      <c r="AU31" s="22"/>
-      <c r="AV31" s="22"/>
-    </row>
-    <row r="32" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="47"/>
-      <c r="X32" s="22"/>
-      <c r="Y32" s="34" t="str">
+    </row>
+    <row r="32" spans="23:31" x14ac:dyDescent="0.35">
+      <c r="W32" s="34"/>
+      <c r="Y32" s="39" t="str">
         <v>C0015</v>
       </c>
-      <c r="Z32" s="32">
+      <c r="Z32" s="42">
         <v>1138</v>
       </c>
-      <c r="AA32" s="32">
+      <c r="AA32" s="42">
         <v>1898</v>
       </c>
-      <c r="AB32" s="32">
+      <c r="AB32" s="42">
         <v>1482</v>
       </c>
-      <c r="AC32" s="32">
+      <c r="AC32" s="42">
         <v>846</v>
       </c>
-      <c r="AD32" s="32">
+      <c r="AD32" s="42">
         <v>1154</v>
       </c>
-      <c r="AE32" s="35">
+      <c r="AE32" s="43">
         <v>6518</v>
       </c>
-      <c r="AF32" s="22"/>
-      <c r="AG32" s="22"/>
-      <c r="AH32" s="22"/>
-      <c r="AI32" s="22"/>
-      <c r="AJ32" s="22"/>
-      <c r="AK32" s="22"/>
-      <c r="AL32" s="22"/>
-      <c r="AM32" s="22"/>
-      <c r="AN32" s="22"/>
-      <c r="AO32" s="22"/>
-      <c r="AP32" s="22"/>
-      <c r="AQ32" s="22"/>
-      <c r="AR32" s="22"/>
-      <c r="AS32" s="22"/>
-      <c r="AT32" s="22"/>
-      <c r="AU32" s="22"/>
-      <c r="AV32" s="22"/>
-    </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="22"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="22"/>
-      <c r="W33" s="47"/>
-      <c r="X33" s="22"/>
-      <c r="Y33" s="42" t="str">
+    </row>
+    <row r="33" spans="22:31" x14ac:dyDescent="0.35">
+      <c r="W33" s="34"/>
+      <c r="Y33" s="39" t="str">
         <v>Columbus</v>
       </c>
-      <c r="Z33" s="32" t="str">
+      <c r="Z33" s="42" t="str">
         <v/>
       </c>
-      <c r="AA33" s="32" t="str">
+      <c r="AA33" s="42" t="str">
         <v/>
       </c>
-      <c r="AB33" s="32" t="str">
+      <c r="AB33" s="42" t="str">
         <v/>
       </c>
-      <c r="AC33" s="32" t="str">
+      <c r="AC33" s="42" t="str">
         <v/>
       </c>
-      <c r="AD33" s="32" t="str">
+      <c r="AD33" s="42" t="str">
         <v/>
       </c>
-      <c r="AE33" s="35" t="str">
+      <c r="AE33" s="43" t="str">
         <v/>
       </c>
-      <c r="AF33" s="22"/>
-      <c r="AG33" s="22"/>
-      <c r="AH33" s="22"/>
-      <c r="AI33" s="22"/>
-      <c r="AJ33" s="22"/>
-      <c r="AK33" s="22"/>
-      <c r="AL33" s="22"/>
-      <c r="AM33" s="22"/>
-      <c r="AN33" s="22"/>
-      <c r="AO33" s="22"/>
-      <c r="AP33" s="22"/>
-      <c r="AQ33" s="22"/>
-      <c r="AR33" s="22"/>
-      <c r="AS33" s="22"/>
-      <c r="AT33" s="22"/>
-      <c r="AU33" s="22"/>
-      <c r="AV33" s="22"/>
-    </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="22"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="22"/>
-      <c r="Y34" s="34" t="str">
+    </row>
+    <row r="34" spans="22:31" x14ac:dyDescent="0.35">
+      <c r="W34" s="34"/>
+      <c r="Y34" s="39" t="str">
         <v>C0001</v>
       </c>
-      <c r="Z34" s="32">
+      <c r="Z34" s="42">
         <v>1655</v>
       </c>
-      <c r="AA34" s="32">
+      <c r="AA34" s="42">
         <v>805</v>
       </c>
-      <c r="AB34" s="32">
+      <c r="AB34" s="42">
         <v>2263</v>
       </c>
-      <c r="AC34" s="32">
+      <c r="AC34" s="42">
         <v>987</v>
       </c>
-      <c r="AD34" s="32">
+      <c r="AD34" s="42">
         <v>1075</v>
       </c>
-      <c r="AE34" s="35">
+      <c r="AE34" s="43">
         <v>6785</v>
       </c>
-      <c r="AF34" s="22"/>
-      <c r="AG34" s="22"/>
-      <c r="AH34" s="22"/>
-      <c r="AI34" s="22"/>
-      <c r="AJ34" s="22"/>
-      <c r="AK34" s="22"/>
-      <c r="AL34" s="22"/>
-      <c r="AM34" s="22"/>
-      <c r="AN34" s="22"/>
-      <c r="AO34" s="22"/>
-      <c r="AP34" s="22"/>
-      <c r="AQ34" s="22"/>
-      <c r="AR34" s="22"/>
-      <c r="AS34" s="22"/>
-      <c r="AT34" s="22"/>
-      <c r="AU34" s="22"/>
-      <c r="AV34" s="22"/>
-    </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="44"/>
-      <c r="W35" s="45" t="str">
+    </row>
+    <row r="35" spans="22:31" x14ac:dyDescent="0.35">
+      <c r="V35" s="35"/>
+      <c r="W35" s="31" t="str">
         <f>'Pivots '!M66</f>
-        <v>% of calls :19%</v>
-      </c>
-      <c r="X35" s="45"/>
-      <c r="Y35" s="34" t="str">
+        <v>% of calls :21%</v>
+      </c>
+      <c r="X35" s="31"/>
+      <c r="Y35" s="39" t="str">
         <v>C0005</v>
       </c>
-      <c r="Z35" s="32">
+      <c r="Z35" s="42">
         <v>1104</v>
       </c>
-      <c r="AA35" s="32">
+      <c r="AA35" s="42">
         <v>2280</v>
       </c>
-      <c r="AB35" s="32">
+      <c r="AB35" s="42">
         <v>1445</v>
       </c>
-      <c r="AC35" s="32">
+      <c r="AC35" s="42">
         <v>1722</v>
       </c>
-      <c r="AD35" s="32">
+      <c r="AD35" s="42">
         <v>1196</v>
       </c>
-      <c r="AE35" s="35">
+      <c r="AE35" s="43">
         <v>7747</v>
       </c>
-      <c r="AF35" s="22"/>
-      <c r="AG35" s="22"/>
-      <c r="AH35" s="22"/>
-      <c r="AI35" s="22"/>
-      <c r="AJ35" s="22"/>
-      <c r="AK35" s="22"/>
-      <c r="AL35" s="22"/>
-      <c r="AM35" s="22"/>
-      <c r="AN35" s="22"/>
-      <c r="AO35" s="22"/>
-      <c r="AP35" s="22"/>
-      <c r="AQ35" s="22"/>
-      <c r="AR35" s="22"/>
-      <c r="AS35" s="22"/>
-      <c r="AT35" s="22"/>
-      <c r="AU35" s="22"/>
-      <c r="AV35" s="22"/>
-    </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="22"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="44"/>
-      <c r="W36" s="45" t="str">
+    </row>
+    <row r="36" spans="22:31" x14ac:dyDescent="0.35">
+      <c r="V36" s="35"/>
+      <c r="W36" s="31" t="str">
         <f>'Pivots '!M67</f>
-        <v>call rank:5</v>
-      </c>
-      <c r="X36" s="45"/>
-      <c r="Y36" s="34" t="str">
+        <v>call rank:2</v>
+      </c>
+      <c r="X36" s="31"/>
+      <c r="Y36" s="39" t="str">
         <v>C0006</v>
       </c>
-      <c r="Z36" s="32">
+      <c r="Z36" s="42">
         <v>372</v>
       </c>
-      <c r="AA36" s="32">
+      <c r="AA36" s="42">
         <v>1818</v>
       </c>
-      <c r="AB36" s="32">
+      <c r="AB36" s="42">
         <v>1346</v>
       </c>
-      <c r="AC36" s="32">
+      <c r="AC36" s="42">
         <v>1156</v>
       </c>
-      <c r="AD36" s="32">
+      <c r="AD36" s="42">
         <v>1484</v>
       </c>
-      <c r="AE36" s="35">
+      <c r="AE36" s="43">
         <v>6176</v>
       </c>
-      <c r="AF36" s="22"/>
-      <c r="AG36" s="22"/>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="22"/>
-      <c r="AJ36" s="22"/>
-      <c r="AK36" s="22"/>
-      <c r="AL36" s="22"/>
-      <c r="AM36" s="22"/>
-      <c r="AN36" s="22"/>
-      <c r="AO36" s="22"/>
-      <c r="AP36" s="22"/>
-      <c r="AQ36" s="22"/>
-      <c r="AR36" s="22"/>
-      <c r="AS36" s="22"/>
-      <c r="AT36" s="22"/>
-      <c r="AU36" s="22"/>
-      <c r="AV36" s="22"/>
-    </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="22"/>
-      <c r="S37" s="22"/>
-      <c r="T37" s="22"/>
-      <c r="U37" s="22"/>
-      <c r="V37" s="44"/>
-      <c r="W37" s="45" t="str">
+    </row>
+    <row r="37" spans="22:31" x14ac:dyDescent="0.35">
+      <c r="V37" s="35"/>
+      <c r="W37" s="31" t="str">
         <f>'Pivots '!M68</f>
-        <v>amount rank:5</v>
-      </c>
-      <c r="X37" s="45"/>
-      <c r="Y37" s="34" t="str">
+        <v>amount rank:1</v>
+      </c>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="39" t="str">
         <v>C0009</v>
       </c>
-      <c r="Z37" s="32">
+      <c r="Z37" s="42">
         <v>1415</v>
       </c>
-      <c r="AA37" s="32">
+      <c r="AA37" s="42">
         <v>1271</v>
       </c>
-      <c r="AB37" s="32">
+      <c r="AB37" s="42">
         <v>1214</v>
       </c>
-      <c r="AC37" s="32">
+      <c r="AC37" s="42">
         <v>1135</v>
       </c>
-      <c r="AD37" s="32">
+      <c r="AD37" s="42">
         <v>1566</v>
       </c>
-      <c r="AE37" s="35">
+      <c r="AE37" s="43">
         <v>6601</v>
       </c>
-      <c r="AF37" s="22"/>
-      <c r="AG37" s="22"/>
-      <c r="AH37" s="22"/>
-      <c r="AI37" s="22"/>
-      <c r="AJ37" s="22"/>
-      <c r="AK37" s="22"/>
-      <c r="AL37" s="22"/>
-      <c r="AM37" s="22"/>
-      <c r="AN37" s="22"/>
-      <c r="AO37" s="22"/>
-      <c r="AP37" s="22"/>
-      <c r="AQ37" s="22"/>
-      <c r="AR37" s="22"/>
-      <c r="AS37" s="22"/>
-      <c r="AT37" s="22"/>
-      <c r="AU37" s="22"/>
-      <c r="AV37" s="22"/>
-    </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="22"/>
-      <c r="P38" s="22"/>
-      <c r="Q38" s="22"/>
-      <c r="R38" s="22"/>
-      <c r="S38" s="22"/>
-      <c r="T38" s="22"/>
-      <c r="U38" s="22"/>
-      <c r="V38" s="22"/>
-      <c r="W38" s="22"/>
-      <c r="X38" s="22"/>
-      <c r="Y38" s="36" t="str">
+    </row>
+    <row r="38" spans="22:31" x14ac:dyDescent="0.35">
+      <c r="Y38" s="44" t="str">
         <v>C0014</v>
       </c>
-      <c r="Z38" s="37">
+      <c r="Z38" s="45">
         <v>1362</v>
       </c>
-      <c r="AA38" s="37">
+      <c r="AA38" s="45">
         <v>1363</v>
       </c>
-      <c r="AB38" s="37">
+      <c r="AB38" s="45">
         <v>1152</v>
       </c>
-      <c r="AC38" s="37">
+      <c r="AC38" s="45">
         <v>777</v>
       </c>
-      <c r="AD38" s="37">
+      <c r="AD38" s="45">
         <v>750</v>
       </c>
-      <c r="AE38" s="38">
+      <c r="AE38" s="46">
         <v>5404</v>
       </c>
-      <c r="AF38" s="22"/>
-      <c r="AG38" s="22"/>
-      <c r="AH38" s="22"/>
-      <c r="AI38" s="22"/>
-      <c r="AJ38" s="22"/>
-      <c r="AK38" s="22"/>
-      <c r="AL38" s="22"/>
-      <c r="AM38" s="22"/>
-      <c r="AN38" s="22"/>
-      <c r="AO38" s="22"/>
-      <c r="AP38" s="22"/>
-      <c r="AQ38" s="22"/>
-      <c r="AR38" s="22"/>
-      <c r="AS38" s="22"/>
-      <c r="AT38" s="22"/>
-      <c r="AU38" s="22"/>
-      <c r="AV38" s="22"/>
-    </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="22"/>
-      <c r="Q39" s="22"/>
-      <c r="R39" s="22"/>
-      <c r="S39" s="22"/>
-      <c r="T39" s="22"/>
-      <c r="U39" s="22"/>
-      <c r="V39" s="22"/>
-      <c r="W39" s="22"/>
-      <c r="X39" s="22"/>
-      <c r="Y39" s="22"/>
-      <c r="Z39" s="22"/>
-      <c r="AA39" s="22"/>
-      <c r="AB39" s="22"/>
-      <c r="AC39" s="22"/>
-      <c r="AD39" s="22"/>
-      <c r="AE39" s="22"/>
-      <c r="AF39" s="22"/>
-      <c r="AG39" s="22"/>
-      <c r="AH39" s="22"/>
-      <c r="AI39" s="22"/>
-      <c r="AJ39" s="22"/>
-      <c r="AK39" s="22"/>
-      <c r="AL39" s="22"/>
-      <c r="AM39" s="22"/>
-      <c r="AN39" s="22"/>
-      <c r="AO39" s="22"/>
-      <c r="AP39" s="22"/>
-      <c r="AQ39" s="22"/>
-      <c r="AR39" s="22"/>
-      <c r="AS39" s="22"/>
-      <c r="AT39" s="22"/>
-      <c r="AU39" s="22"/>
-      <c r="AV39" s="22"/>
-    </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="22"/>
-      <c r="P40" s="22"/>
-      <c r="Q40" s="22"/>
-      <c r="R40" s="22"/>
-      <c r="S40" s="22"/>
-      <c r="T40" s="22"/>
-      <c r="U40" s="22"/>
-      <c r="V40" s="22"/>
-      <c r="W40" s="22"/>
-      <c r="X40" s="22"/>
-      <c r="Y40" s="22"/>
-      <c r="Z40" s="22"/>
-      <c r="AA40" s="22"/>
-      <c r="AB40" s="22"/>
-      <c r="AC40" s="22"/>
-      <c r="AD40" s="22"/>
-      <c r="AE40" s="22"/>
-      <c r="AF40" s="22"/>
-      <c r="AG40" s="22"/>
-      <c r="AH40" s="22"/>
-      <c r="AI40" s="22"/>
-      <c r="AJ40" s="22"/>
-      <c r="AK40" s="22"/>
-      <c r="AL40" s="22"/>
-      <c r="AM40" s="22"/>
-      <c r="AN40" s="22"/>
-      <c r="AO40" s="22"/>
-      <c r="AP40" s="22"/>
-      <c r="AQ40" s="22"/>
-      <c r="AR40" s="22"/>
-      <c r="AS40" s="22"/>
-      <c r="AT40" s="22"/>
-      <c r="AU40" s="22"/>
-      <c r="AV40" s="22"/>
-    </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="22"/>
-      <c r="O41" s="22"/>
-      <c r="P41" s="22"/>
-      <c r="Q41" s="22"/>
-      <c r="R41" s="22"/>
-      <c r="S41" s="22"/>
-      <c r="T41" s="22"/>
-      <c r="U41" s="22"/>
-      <c r="V41" s="22"/>
-      <c r="W41" s="22"/>
-      <c r="X41" s="22"/>
-      <c r="Y41" s="22"/>
-      <c r="Z41" s="22"/>
-      <c r="AA41" s="22"/>
-      <c r="AB41" s="22"/>
-      <c r="AC41" s="22"/>
-      <c r="AD41" s="22"/>
-      <c r="AE41" s="22"/>
-      <c r="AF41" s="22"/>
-      <c r="AG41" s="22"/>
-      <c r="AH41" s="22"/>
-      <c r="AI41" s="22"/>
-      <c r="AJ41" s="22"/>
-      <c r="AK41" s="22"/>
-      <c r="AL41" s="22"/>
-      <c r="AM41" s="22"/>
-      <c r="AN41" s="22"/>
-      <c r="AO41" s="22"/>
-      <c r="AP41" s="22"/>
-      <c r="AQ41" s="22"/>
-      <c r="AR41" s="22"/>
-      <c r="AS41" s="22"/>
-      <c r="AT41" s="22"/>
-      <c r="AU41" s="22"/>
-      <c r="AV41" s="22"/>
-    </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="22"/>
-      <c r="Q42" s="22"/>
-      <c r="R42" s="22"/>
-      <c r="S42" s="22"/>
-      <c r="T42" s="22"/>
-      <c r="U42" s="22"/>
-      <c r="V42" s="22"/>
-      <c r="W42" s="22"/>
-      <c r="X42" s="22"/>
-      <c r="Y42" s="22"/>
-      <c r="Z42" s="22"/>
-      <c r="AA42" s="22"/>
-      <c r="AB42" s="22"/>
-      <c r="AC42" s="22"/>
-      <c r="AD42" s="22"/>
-      <c r="AE42" s="22"/>
-      <c r="AF42" s="22"/>
-      <c r="AG42" s="22"/>
-      <c r="AH42" s="22"/>
-      <c r="AI42" s="22"/>
-      <c r="AJ42" s="22"/>
-      <c r="AK42" s="22"/>
-      <c r="AL42" s="22"/>
-      <c r="AM42" s="22"/>
-      <c r="AN42" s="22"/>
-      <c r="AO42" s="22"/>
-      <c r="AP42" s="22"/>
-      <c r="AQ42" s="22"/>
-      <c r="AR42" s="22"/>
-      <c r="AS42" s="22"/>
-      <c r="AT42" s="22"/>
-      <c r="AU42" s="22"/>
-      <c r="AV42" s="22"/>
-    </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="22"/>
-      <c r="O43" s="22"/>
-      <c r="P43" s="22"/>
-      <c r="Q43" s="22"/>
-      <c r="R43" s="22"/>
-      <c r="S43" s="22"/>
-      <c r="T43" s="22"/>
-      <c r="U43" s="22"/>
-      <c r="V43" s="22"/>
-      <c r="W43" s="22"/>
-      <c r="X43" s="22"/>
-      <c r="Y43" s="22"/>
-      <c r="Z43" s="22"/>
-      <c r="AA43" s="22"/>
-      <c r="AB43" s="22"/>
-      <c r="AC43" s="22"/>
-      <c r="AD43" s="22"/>
-      <c r="AE43" s="22"/>
-      <c r="AF43" s="22"/>
-      <c r="AG43" s="22"/>
-      <c r="AH43" s="22"/>
-      <c r="AI43" s="22"/>
-      <c r="AJ43" s="22"/>
-      <c r="AK43" s="22"/>
-      <c r="AL43" s="22"/>
-      <c r="AM43" s="22"/>
-      <c r="AN43" s="22"/>
-      <c r="AO43" s="22"/>
-      <c r="AP43" s="22"/>
-      <c r="AQ43" s="22"/>
-      <c r="AR43" s="22"/>
-      <c r="AS43" s="22"/>
-      <c r="AT43" s="22"/>
-      <c r="AU43" s="22"/>
-      <c r="AV43" s="22"/>
-    </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22"/>
-      <c r="P44" s="22"/>
-      <c r="Q44" s="22"/>
-      <c r="R44" s="22"/>
-      <c r="S44" s="22"/>
-      <c r="T44" s="22"/>
-      <c r="U44" s="22"/>
-      <c r="V44" s="22"/>
-      <c r="W44" s="22"/>
-      <c r="X44" s="22"/>
-      <c r="Y44" s="22"/>
-      <c r="Z44" s="22"/>
-      <c r="AA44" s="22"/>
-      <c r="AB44" s="22"/>
-      <c r="AC44" s="22"/>
-      <c r="AD44" s="22"/>
-      <c r="AE44" s="22"/>
-      <c r="AF44" s="22"/>
-      <c r="AG44" s="22"/>
-      <c r="AH44" s="22"/>
-      <c r="AI44" s="22"/>
-      <c r="AJ44" s="22"/>
-      <c r="AK44" s="22"/>
-      <c r="AL44" s="22"/>
-      <c r="AM44" s="22"/>
-      <c r="AN44" s="22"/>
-      <c r="AO44" s="22"/>
-      <c r="AP44" s="22"/>
-      <c r="AQ44" s="22"/>
-      <c r="AR44" s="22"/>
-      <c r="AS44" s="22"/>
-      <c r="AT44" s="22"/>
-      <c r="AU44" s="22"/>
-      <c r="AV44" s="22"/>
-    </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="22"/>
-      <c r="O45" s="22"/>
-      <c r="P45" s="22"/>
-      <c r="Q45" s="22"/>
-      <c r="R45" s="22"/>
-      <c r="S45" s="22"/>
-      <c r="T45" s="22"/>
-      <c r="U45" s="22"/>
-      <c r="V45" s="22"/>
-      <c r="W45" s="22"/>
-      <c r="X45" s="22"/>
-      <c r="Y45" s="22"/>
-      <c r="Z45" s="22"/>
-      <c r="AA45" s="22"/>
-      <c r="AB45" s="22"/>
-      <c r="AC45" s="22"/>
-      <c r="AD45" s="22"/>
-      <c r="AE45" s="22"/>
-      <c r="AF45" s="22"/>
-      <c r="AG45" s="22"/>
-      <c r="AH45" s="22"/>
-      <c r="AI45" s="22"/>
-      <c r="AJ45" s="22"/>
-      <c r="AK45" s="22"/>
-      <c r="AL45" s="22"/>
-      <c r="AM45" s="22"/>
-      <c r="AN45" s="22"/>
-      <c r="AO45" s="22"/>
-      <c r="AP45" s="22"/>
-      <c r="AQ45" s="22"/>
-      <c r="AR45" s="22"/>
-      <c r="AS45" s="22"/>
-      <c r="AT45" s="22"/>
-      <c r="AU45" s="22"/>
-      <c r="AV45" s="22"/>
-    </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="22"/>
-      <c r="R46" s="22"/>
-      <c r="S46" s="22"/>
-      <c r="T46" s="22"/>
-      <c r="U46" s="22"/>
-      <c r="V46" s="22"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="22"/>
-      <c r="Y46" s="22"/>
-      <c r="Z46" s="22"/>
-      <c r="AA46" s="22"/>
-      <c r="AB46" s="22"/>
-      <c r="AC46" s="22"/>
-      <c r="AD46" s="22"/>
-      <c r="AE46" s="22"/>
-      <c r="AF46" s="22"/>
-      <c r="AG46" s="22"/>
-      <c r="AH46" s="22"/>
-      <c r="AI46" s="22"/>
-      <c r="AJ46" s="22"/>
-      <c r="AK46" s="22"/>
-      <c r="AL46" s="22"/>
-      <c r="AM46" s="22"/>
-      <c r="AN46" s="22"/>
-      <c r="AO46" s="22"/>
-      <c r="AP46" s="22"/>
-      <c r="AQ46" s="22"/>
-      <c r="AR46" s="22"/>
-      <c r="AS46" s="22"/>
-      <c r="AT46" s="22"/>
-      <c r="AU46" s="22"/>
-      <c r="AV46" s="22"/>
-    </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-      <c r="P47" s="22"/>
-      <c r="Q47" s="22"/>
-      <c r="R47" s="22"/>
-      <c r="S47" s="22"/>
-      <c r="T47" s="22"/>
-      <c r="U47" s="22"/>
-      <c r="V47" s="22"/>
-      <c r="W47" s="22"/>
-      <c r="X47" s="22"/>
-      <c r="Y47" s="22"/>
-      <c r="Z47" s="22"/>
-      <c r="AA47" s="22"/>
-      <c r="AB47" s="22"/>
-      <c r="AC47" s="22"/>
-      <c r="AD47" s="22"/>
-      <c r="AE47" s="22"/>
-      <c r="AF47" s="22"/>
-      <c r="AG47" s="22"/>
-      <c r="AH47" s="22"/>
-      <c r="AI47" s="22"/>
-      <c r="AJ47" s="22"/>
-      <c r="AK47" s="22"/>
-      <c r="AL47" s="22"/>
-      <c r="AM47" s="22"/>
-      <c r="AN47" s="22"/>
-      <c r="AO47" s="22"/>
-      <c r="AP47" s="22"/>
-      <c r="AQ47" s="22"/>
-      <c r="AR47" s="22"/>
-      <c r="AS47" s="22"/>
-      <c r="AT47" s="22"/>
-      <c r="AU47" s="22"/>
-      <c r="AV47" s="22"/>
-    </row>
-    <row r="48" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="22"/>
-      <c r="O48" s="22"/>
-      <c r="P48" s="22"/>
-      <c r="Q48" s="22"/>
-      <c r="R48" s="22"/>
-      <c r="S48" s="22"/>
-      <c r="T48" s="22"/>
-      <c r="U48" s="22"/>
-      <c r="V48" s="22"/>
-      <c r="W48" s="22"/>
-      <c r="X48" s="22"/>
-      <c r="Y48" s="22"/>
-      <c r="Z48" s="22"/>
-      <c r="AA48" s="22"/>
-      <c r="AB48" s="22"/>
-      <c r="AC48" s="22"/>
-      <c r="AD48" s="22"/>
-      <c r="AE48" s="22"/>
-      <c r="AF48" s="22"/>
-      <c r="AG48" s="22"/>
-      <c r="AH48" s="22"/>
-      <c r="AI48" s="22"/>
-      <c r="AJ48" s="22"/>
-      <c r="AK48" s="22"/>
-      <c r="AL48" s="22"/>
-      <c r="AM48" s="22"/>
-      <c r="AN48" s="22"/>
-      <c r="AO48" s="22"/>
-      <c r="AP48" s="22"/>
-      <c r="AQ48" s="22"/>
-      <c r="AR48" s="22"/>
-      <c r="AS48" s="22"/>
-      <c r="AT48" s="22"/>
-      <c r="AU48" s="22"/>
-      <c r="AV48" s="22"/>
-    </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="22"/>
-      <c r="L49" s="22"/>
-      <c r="M49" s="22"/>
-      <c r="N49" s="22"/>
-      <c r="O49" s="22"/>
-      <c r="P49" s="22"/>
-      <c r="Q49" s="22"/>
-      <c r="R49" s="22"/>
-      <c r="S49" s="22"/>
-      <c r="T49" s="22"/>
-      <c r="U49" s="22"/>
-      <c r="V49" s="22"/>
-      <c r="W49" s="22"/>
-      <c r="X49" s="22"/>
-      <c r="Y49" s="22"/>
-      <c r="Z49" s="22"/>
-      <c r="AA49" s="22"/>
-      <c r="AB49" s="22"/>
-      <c r="AC49" s="22"/>
-      <c r="AD49" s="22"/>
-      <c r="AE49" s="22"/>
-      <c r="AF49" s="22"/>
-      <c r="AG49" s="22"/>
-      <c r="AH49" s="22"/>
-      <c r="AI49" s="22"/>
-      <c r="AJ49" s="22"/>
-      <c r="AK49" s="22"/>
-      <c r="AL49" s="22"/>
-      <c r="AM49" s="22"/>
-      <c r="AN49" s="22"/>
-      <c r="AO49" s="22"/>
-      <c r="AP49" s="22"/>
-      <c r="AQ49" s="22"/>
-      <c r="AR49" s="22"/>
-      <c r="AS49" s="22"/>
-      <c r="AT49" s="22"/>
-      <c r="AU49" s="22"/>
-      <c r="AV49" s="22"/>
-    </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="22"/>
-      <c r="L50" s="22"/>
-      <c r="M50" s="22"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="22"/>
-      <c r="P50" s="22"/>
-      <c r="Q50" s="22"/>
-      <c r="R50" s="22"/>
-      <c r="S50" s="22"/>
-      <c r="T50" s="22"/>
-      <c r="U50" s="22"/>
-      <c r="V50" s="22"/>
-      <c r="W50" s="22"/>
-      <c r="X50" s="22"/>
-      <c r="Y50" s="22"/>
-      <c r="Z50" s="22"/>
-      <c r="AA50" s="22"/>
-      <c r="AB50" s="22"/>
-      <c r="AC50" s="22"/>
-      <c r="AD50" s="22"/>
-      <c r="AE50" s="22"/>
-      <c r="AF50" s="22"/>
-      <c r="AG50" s="22"/>
-      <c r="AH50" s="22"/>
-      <c r="AI50" s="22"/>
-      <c r="AJ50" s="22"/>
-      <c r="AK50" s="22"/>
-      <c r="AL50" s="22"/>
-      <c r="AM50" s="22"/>
-      <c r="AN50" s="22"/>
-      <c r="AO50" s="22"/>
-      <c r="AP50" s="22"/>
-      <c r="AQ50" s="22"/>
-      <c r="AR50" s="22"/>
-      <c r="AS50" s="22"/>
-      <c r="AT50" s="22"/>
-      <c r="AU50" s="22"/>
-      <c r="AV50" s="22"/>
-    </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A51" s="22"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="22"/>
-      <c r="J51" s="22"/>
-      <c r="K51" s="22"/>
-      <c r="L51" s="22"/>
-      <c r="M51" s="22"/>
-      <c r="N51" s="22"/>
-      <c r="O51" s="22"/>
-      <c r="P51" s="22"/>
-      <c r="Q51" s="22"/>
-      <c r="R51" s="22"/>
-      <c r="S51" s="22"/>
-      <c r="T51" s="22"/>
-      <c r="U51" s="22"/>
-      <c r="V51" s="22"/>
-      <c r="W51" s="22"/>
-      <c r="X51" s="22"/>
-      <c r="Y51" s="22"/>
-      <c r="Z51" s="22"/>
-      <c r="AA51" s="22"/>
-      <c r="AB51" s="22"/>
-      <c r="AC51" s="22"/>
-      <c r="AD51" s="22"/>
-      <c r="AE51" s="22"/>
-      <c r="AF51" s="22"/>
-      <c r="AG51" s="22"/>
-      <c r="AH51" s="22"/>
-      <c r="AI51" s="22"/>
-      <c r="AJ51" s="22"/>
-      <c r="AK51" s="22"/>
-      <c r="AL51" s="22"/>
-      <c r="AM51" s="22"/>
-      <c r="AN51" s="22"/>
-      <c r="AO51" s="22"/>
-      <c r="AP51" s="22"/>
-      <c r="AQ51" s="22"/>
-      <c r="AR51" s="22"/>
-      <c r="AS51" s="22"/>
-      <c r="AT51" s="22"/>
-      <c r="AU51" s="22"/>
-      <c r="AV51" s="22"/>
-    </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A52" s="22"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
-      <c r="J52" s="22"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="22"/>
-      <c r="N52" s="22"/>
-      <c r="O52" s="22"/>
-      <c r="P52" s="22"/>
-      <c r="Q52" s="22"/>
-      <c r="R52" s="22"/>
-      <c r="S52" s="22"/>
-      <c r="T52" s="22"/>
-      <c r="U52" s="22"/>
-      <c r="V52" s="22"/>
-      <c r="W52" s="22"/>
-      <c r="X52" s="22"/>
-      <c r="Y52" s="22"/>
-      <c r="Z52" s="22"/>
-      <c r="AA52" s="22"/>
-      <c r="AB52" s="22"/>
-      <c r="AC52" s="22"/>
-      <c r="AD52" s="22"/>
-      <c r="AE52" s="22"/>
-      <c r="AF52" s="22"/>
-      <c r="AG52" s="22"/>
-      <c r="AH52" s="22"/>
-      <c r="AI52" s="22"/>
-      <c r="AJ52" s="22"/>
-      <c r="AK52" s="22"/>
-      <c r="AL52" s="22"/>
-      <c r="AM52" s="22"/>
-      <c r="AN52" s="22"/>
-      <c r="AO52" s="22"/>
-      <c r="AP52" s="22"/>
-      <c r="AQ52" s="22"/>
-      <c r="AR52" s="22"/>
-      <c r="AS52" s="22"/>
-      <c r="AT52" s="22"/>
-      <c r="AU52" s="22"/>
-      <c r="AV52" s="22"/>
-    </row>
-    <row r="53" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="22"/>
-      <c r="K53" s="22"/>
-      <c r="L53" s="22"/>
-      <c r="M53" s="22"/>
-      <c r="N53" s="22"/>
-      <c r="O53" s="22"/>
-      <c r="P53" s="22"/>
-      <c r="Q53" s="22"/>
-      <c r="R53" s="22"/>
-      <c r="S53" s="22"/>
-      <c r="T53" s="22"/>
-      <c r="U53" s="22"/>
-      <c r="V53" s="22"/>
-      <c r="W53" s="22"/>
-      <c r="X53" s="22"/>
-      <c r="Y53" s="22"/>
-      <c r="Z53" s="22"/>
-      <c r="AA53" s="22"/>
-      <c r="AB53" s="22"/>
-      <c r="AC53" s="22"/>
-      <c r="AD53" s="22"/>
-      <c r="AE53" s="22"/>
-      <c r="AF53" s="22"/>
-      <c r="AG53" s="22"/>
-      <c r="AH53" s="22"/>
-      <c r="AI53" s="22"/>
-      <c r="AJ53" s="22"/>
-      <c r="AK53" s="22"/>
-      <c r="AL53" s="22"/>
-      <c r="AM53" s="22"/>
-      <c r="AN53" s="22"/>
-      <c r="AO53" s="22"/>
-      <c r="AP53" s="22"/>
-      <c r="AQ53" s="22"/>
-      <c r="AR53" s="22"/>
-      <c r="AS53" s="22"/>
-      <c r="AT53" s="22"/>
-      <c r="AU53" s="22"/>
-      <c r="AV53" s="22"/>
-    </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
-      <c r="O54" s="22"/>
-      <c r="P54" s="22"/>
-      <c r="Q54" s="22"/>
-      <c r="R54" s="22"/>
-      <c r="S54" s="22"/>
-      <c r="T54" s="22"/>
-      <c r="U54" s="22"/>
-      <c r="V54" s="22"/>
-      <c r="W54" s="22"/>
-      <c r="X54" s="22"/>
-      <c r="Y54" s="22"/>
-      <c r="Z54" s="22"/>
-      <c r="AA54" s="22"/>
-      <c r="AB54" s="22"/>
-      <c r="AC54" s="22"/>
-      <c r="AD54" s="22"/>
-      <c r="AE54" s="22"/>
-      <c r="AF54" s="22"/>
-      <c r="AG54" s="22"/>
-      <c r="AH54" s="22"/>
-      <c r="AI54" s="22"/>
-      <c r="AJ54" s="22"/>
-      <c r="AK54" s="22"/>
-      <c r="AL54" s="22"/>
-      <c r="AM54" s="22"/>
-      <c r="AN54" s="22"/>
-      <c r="AO54" s="22"/>
-      <c r="AP54" s="22"/>
-      <c r="AQ54" s="22"/>
-      <c r="AR54" s="22"/>
-      <c r="AS54" s="22"/>
-      <c r="AT54" s="22"/>
-      <c r="AU54" s="22"/>
-      <c r="AV54" s="22"/>
-    </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
-      <c r="J55" s="22"/>
-      <c r="K55" s="22"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="22"/>
-      <c r="N55" s="22"/>
-      <c r="O55" s="22"/>
-      <c r="P55" s="22"/>
-      <c r="Q55" s="22"/>
-      <c r="R55" s="22"/>
-      <c r="S55" s="22"/>
-      <c r="T55" s="22"/>
-      <c r="U55" s="22"/>
-      <c r="V55" s="22"/>
-      <c r="W55" s="22"/>
-      <c r="X55" s="22"/>
-      <c r="Y55" s="22"/>
-      <c r="Z55" s="22"/>
-      <c r="AA55" s="22"/>
-      <c r="AB55" s="22"/>
-      <c r="AC55" s="22"/>
-      <c r="AD55" s="22"/>
-      <c r="AE55" s="22"/>
-      <c r="AF55" s="22"/>
-      <c r="AG55" s="22"/>
-      <c r="AH55" s="22"/>
-      <c r="AI55" s="22"/>
-      <c r="AJ55" s="22"/>
-      <c r="AK55" s="22"/>
-      <c r="AL55" s="22"/>
-      <c r="AM55" s="22"/>
-      <c r="AN55" s="22"/>
-      <c r="AO55" s="22"/>
-      <c r="AP55" s="22"/>
-      <c r="AQ55" s="22"/>
-      <c r="AR55" s="22"/>
-      <c r="AS55" s="22"/>
-      <c r="AT55" s="22"/>
-      <c r="AU55" s="22"/>
-      <c r="AV55" s="22"/>
-    </row>
-    <row r="56" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
-      <c r="J56" s="22"/>
-      <c r="K56" s="22"/>
-      <c r="L56" s="22"/>
-      <c r="M56" s="22"/>
-      <c r="N56" s="22"/>
-      <c r="O56" s="22"/>
-      <c r="P56" s="22"/>
-      <c r="Q56" s="22"/>
-      <c r="R56" s="22"/>
-      <c r="S56" s="22"/>
-      <c r="T56" s="22"/>
-      <c r="U56" s="22"/>
-      <c r="V56" s="22"/>
-      <c r="W56" s="22"/>
-      <c r="X56" s="22"/>
-      <c r="Y56" s="22"/>
-      <c r="Z56" s="22"/>
-      <c r="AA56" s="22"/>
-      <c r="AB56" s="22"/>
-      <c r="AC56" s="22"/>
-      <c r="AD56" s="22"/>
-      <c r="AE56" s="22"/>
-      <c r="AF56" s="22"/>
-      <c r="AG56" s="22"/>
-      <c r="AH56" s="22"/>
-      <c r="AI56" s="22"/>
-      <c r="AJ56" s="22"/>
-      <c r="AK56" s="22"/>
-      <c r="AL56" s="22"/>
-      <c r="AM56" s="22"/>
-      <c r="AN56" s="22"/>
-      <c r="AO56" s="22"/>
-      <c r="AP56" s="22"/>
-      <c r="AQ56" s="22"/>
-      <c r="AR56" s="22"/>
-      <c r="AS56" s="22"/>
-      <c r="AT56" s="22"/>
-      <c r="AU56" s="22"/>
-      <c r="AV56" s="22"/>
-    </row>
-    <row r="57" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-      <c r="J57" s="22"/>
-      <c r="K57" s="22"/>
-      <c r="L57" s="22"/>
-      <c r="M57" s="22"/>
-      <c r="N57" s="22"/>
-      <c r="O57" s="22"/>
-      <c r="P57" s="22"/>
-      <c r="Q57" s="22"/>
-      <c r="R57" s="22"/>
-      <c r="S57" s="22"/>
-      <c r="T57" s="22"/>
-      <c r="U57" s="22"/>
-      <c r="V57" s="22"/>
-      <c r="W57" s="22"/>
-      <c r="X57" s="22"/>
-      <c r="Y57" s="22"/>
-      <c r="Z57" s="22"/>
-      <c r="AA57" s="22"/>
-      <c r="AB57" s="22"/>
-      <c r="AC57" s="22"/>
-      <c r="AD57" s="22"/>
-      <c r="AE57" s="22"/>
-      <c r="AF57" s="22"/>
-      <c r="AG57" s="22"/>
-      <c r="AH57" s="22"/>
-      <c r="AI57" s="22"/>
-      <c r="AJ57" s="22"/>
-      <c r="AK57" s="22"/>
-      <c r="AL57" s="22"/>
-      <c r="AM57" s="22"/>
-      <c r="AN57" s="22"/>
-      <c r="AO57" s="22"/>
-      <c r="AP57" s="22"/>
-      <c r="AQ57" s="22"/>
-      <c r="AR57" s="22"/>
-      <c r="AS57" s="22"/>
-      <c r="AT57" s="22"/>
-      <c r="AU57" s="22"/>
-      <c r="AV57" s="22"/>
-    </row>
-    <row r="58" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A58" s="22"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="22"/>
-      <c r="N58" s="22"/>
-      <c r="O58" s="22"/>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="22"/>
-      <c r="R58" s="22"/>
-      <c r="S58" s="22"/>
-      <c r="T58" s="22"/>
-      <c r="U58" s="22"/>
-      <c r="V58" s="22"/>
-      <c r="W58" s="22"/>
-      <c r="X58" s="22"/>
-      <c r="Y58" s="22"/>
-      <c r="Z58" s="22"/>
-      <c r="AA58" s="22"/>
-      <c r="AB58" s="22"/>
-      <c r="AC58" s="22"/>
-      <c r="AD58" s="22"/>
-      <c r="AE58" s="22"/>
-      <c r="AF58" s="22"/>
-      <c r="AG58" s="22"/>
-      <c r="AH58" s="22"/>
-      <c r="AI58" s="22"/>
-      <c r="AJ58" s="22"/>
-      <c r="AK58" s="22"/>
-      <c r="AL58" s="22"/>
-      <c r="AM58" s="22"/>
-      <c r="AN58" s="22"/>
-      <c r="AO58" s="22"/>
-      <c r="AP58" s="22"/>
-      <c r="AQ58" s="22"/>
-      <c r="AR58" s="22"/>
-      <c r="AS58" s="22"/>
-      <c r="AT58" s="22"/>
-      <c r="AU58" s="22"/>
-      <c r="AV58" s="22"/>
-    </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="22"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="22"/>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="22"/>
-      <c r="R59" s="22"/>
-      <c r="S59" s="22"/>
-      <c r="T59" s="22"/>
-      <c r="U59" s="22"/>
-      <c r="V59" s="22"/>
-      <c r="W59" s="22"/>
-      <c r="X59" s="22"/>
-      <c r="Y59" s="22"/>
-      <c r="Z59" s="22"/>
-      <c r="AA59" s="22"/>
-      <c r="AB59" s="22"/>
-      <c r="AC59" s="22"/>
-      <c r="AD59" s="22"/>
-      <c r="AE59" s="22"/>
-      <c r="AF59" s="22"/>
-      <c r="AG59" s="22"/>
-      <c r="AH59" s="22"/>
-      <c r="AI59" s="22"/>
-      <c r="AJ59" s="22"/>
-      <c r="AK59" s="22"/>
-      <c r="AL59" s="22"/>
-      <c r="AM59" s="22"/>
-      <c r="AN59" s="22"/>
-      <c r="AO59" s="22"/>
-      <c r="AP59" s="22"/>
-      <c r="AQ59" s="22"/>
-      <c r="AR59" s="22"/>
-      <c r="AS59" s="22"/>
-      <c r="AT59" s="22"/>
-      <c r="AU59" s="22"/>
-      <c r="AV59" s="22"/>
-    </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A60" s="22"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="22"/>
-      <c r="L60" s="22"/>
-      <c r="M60" s="22"/>
-      <c r="N60" s="22"/>
-      <c r="O60" s="22"/>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="22"/>
-      <c r="R60" s="22"/>
-      <c r="S60" s="22"/>
-      <c r="T60" s="22"/>
-      <c r="U60" s="22"/>
-      <c r="V60" s="22"/>
-      <c r="W60" s="22"/>
-      <c r="X60" s="22"/>
-      <c r="Y60" s="22"/>
-      <c r="Z60" s="22"/>
-      <c r="AA60" s="22"/>
-      <c r="AB60" s="22"/>
-      <c r="AC60" s="22"/>
-      <c r="AD60" s="22"/>
-      <c r="AE60" s="22"/>
-      <c r="AF60" s="22"/>
-      <c r="AG60" s="22"/>
-      <c r="AH60" s="22"/>
-      <c r="AI60" s="22"/>
-      <c r="AJ60" s="22"/>
-      <c r="AK60" s="22"/>
-      <c r="AL60" s="22"/>
-      <c r="AM60" s="22"/>
-      <c r="AN60" s="22"/>
-      <c r="AO60" s="22"/>
-      <c r="AP60" s="22"/>
-      <c r="AQ60" s="22"/>
-      <c r="AR60" s="22"/>
-      <c r="AS60" s="22"/>
-      <c r="AT60" s="22"/>
-      <c r="AU60" s="22"/>
-      <c r="AV60" s="22"/>
-    </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
-      <c r="R61" s="22"/>
-      <c r="S61" s="22"/>
-      <c r="T61" s="22"/>
-      <c r="U61" s="22"/>
-      <c r="V61" s="22"/>
-      <c r="W61" s="22"/>
-      <c r="X61" s="22"/>
-      <c r="Y61" s="22"/>
-      <c r="Z61" s="22"/>
-      <c r="AA61" s="22"/>
-      <c r="AB61" s="22"/>
-      <c r="AC61" s="22"/>
-      <c r="AD61" s="22"/>
-      <c r="AE61" s="22"/>
-      <c r="AF61" s="22"/>
-      <c r="AG61" s="22"/>
-      <c r="AH61" s="22"/>
-      <c r="AI61" s="22"/>
-      <c r="AJ61" s="22"/>
-      <c r="AK61" s="22"/>
-      <c r="AL61" s="22"/>
-      <c r="AM61" s="22"/>
-      <c r="AN61" s="22"/>
-      <c r="AO61" s="22"/>
-      <c r="AP61" s="22"/>
-      <c r="AQ61" s="22"/>
-      <c r="AR61" s="22"/>
-      <c r="AS61" s="22"/>
-      <c r="AT61" s="22"/>
-      <c r="AU61" s="22"/>
-      <c r="AV61" s="22"/>
-    </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="22"/>
-      <c r="O62" s="22"/>
-      <c r="P62" s="22"/>
-      <c r="Q62" s="22"/>
-      <c r="R62" s="22"/>
-      <c r="S62" s="22"/>
-      <c r="T62" s="22"/>
-      <c r="U62" s="22"/>
-      <c r="V62" s="22"/>
-      <c r="W62" s="22"/>
-      <c r="X62" s="22"/>
-      <c r="Y62" s="22"/>
-      <c r="Z62" s="22"/>
-      <c r="AA62" s="22"/>
-      <c r="AB62" s="22"/>
-      <c r="AC62" s="22"/>
-      <c r="AD62" s="22"/>
-      <c r="AE62" s="22"/>
-      <c r="AF62" s="22"/>
-      <c r="AG62" s="22"/>
-      <c r="AH62" s="22"/>
-      <c r="AI62" s="22"/>
-      <c r="AJ62" s="22"/>
-      <c r="AK62" s="22"/>
-      <c r="AL62" s="22"/>
-      <c r="AM62" s="22"/>
-      <c r="AN62" s="22"/>
-      <c r="AO62" s="22"/>
-      <c r="AP62" s="22"/>
-      <c r="AQ62" s="22"/>
-      <c r="AR62" s="22"/>
-      <c r="AS62" s="22"/>
-      <c r="AT62" s="22"/>
-      <c r="AU62" s="22"/>
-      <c r="AV62" s="22"/>
-    </row>
-    <row r="63" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="22"/>
-      <c r="N63" s="22"/>
-      <c r="O63" s="22"/>
-      <c r="P63" s="22"/>
-      <c r="Q63" s="22"/>
-      <c r="R63" s="22"/>
-      <c r="S63" s="22"/>
-      <c r="T63" s="22"/>
-      <c r="U63" s="22"/>
-      <c r="V63" s="22"/>
-      <c r="W63" s="22"/>
-      <c r="X63" s="22"/>
-      <c r="Y63" s="22"/>
-      <c r="Z63" s="22"/>
-      <c r="AA63" s="22"/>
-      <c r="AB63" s="22"/>
-      <c r="AC63" s="22"/>
-      <c r="AD63" s="22"/>
-      <c r="AE63" s="22"/>
-      <c r="AF63" s="22"/>
-      <c r="AG63" s="22"/>
-      <c r="AH63" s="22"/>
-      <c r="AI63" s="22"/>
-      <c r="AJ63" s="22"/>
-      <c r="AK63" s="22"/>
-      <c r="AL63" s="22"/>
-      <c r="AM63" s="22"/>
-      <c r="AN63" s="22"/>
-      <c r="AO63" s="22"/>
-      <c r="AP63" s="22"/>
-      <c r="AQ63" s="22"/>
-      <c r="AR63" s="22"/>
-      <c r="AS63" s="22"/>
-      <c r="AT63" s="22"/>
-      <c r="AU63" s="22"/>
-      <c r="AV63" s="22"/>
-    </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
-      <c r="J64" s="22"/>
-      <c r="K64" s="22"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="22"/>
-      <c r="N64" s="22"/>
-      <c r="O64" s="22"/>
-      <c r="P64" s="22"/>
-      <c r="Q64" s="22"/>
-      <c r="R64" s="22"/>
-      <c r="S64" s="22"/>
-      <c r="T64" s="22"/>
-      <c r="U64" s="22"/>
-      <c r="V64" s="22"/>
-      <c r="W64" s="22"/>
-      <c r="X64" s="22"/>
-      <c r="Y64" s="22"/>
-      <c r="Z64" s="22"/>
-      <c r="AA64" s="22"/>
-      <c r="AB64" s="22"/>
-      <c r="AC64" s="22"/>
-      <c r="AD64" s="22"/>
-      <c r="AE64" s="22"/>
-      <c r="AF64" s="22"/>
-      <c r="AG64" s="22"/>
-      <c r="AH64" s="22"/>
-      <c r="AI64" s="22"/>
-      <c r="AJ64" s="22"/>
-      <c r="AK64" s="22"/>
-      <c r="AL64" s="22"/>
-      <c r="AM64" s="22"/>
-      <c r="AN64" s="22"/>
-      <c r="AO64" s="22"/>
-      <c r="AP64" s="22"/>
-      <c r="AQ64" s="22"/>
-      <c r="AR64" s="22"/>
-      <c r="AS64" s="22"/>
-      <c r="AT64" s="22"/>
-      <c r="AU64" s="22"/>
-      <c r="AV64" s="22"/>
-    </row>
-    <row r="65" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A65" s="22"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-      <c r="L65" s="22"/>
-      <c r="M65" s="22"/>
-      <c r="N65" s="22"/>
-      <c r="O65" s="22"/>
-      <c r="P65" s="22"/>
-      <c r="Q65" s="22"/>
-      <c r="R65" s="22"/>
-      <c r="S65" s="22"/>
-      <c r="T65" s="22"/>
-      <c r="U65" s="22"/>
-      <c r="V65" s="22"/>
-      <c r="W65" s="22"/>
-      <c r="X65" s="22"/>
-      <c r="Y65" s="22"/>
-      <c r="Z65" s="22"/>
-      <c r="AA65" s="22"/>
-      <c r="AB65" s="22"/>
-      <c r="AC65" s="22"/>
-      <c r="AD65" s="22"/>
-      <c r="AE65" s="22"/>
-      <c r="AF65" s="22"/>
-      <c r="AG65" s="22"/>
-      <c r="AH65" s="22"/>
-      <c r="AI65" s="22"/>
-      <c r="AJ65" s="22"/>
-      <c r="AK65" s="22"/>
-      <c r="AL65" s="22"/>
-      <c r="AM65" s="22"/>
-      <c r="AN65" s="22"/>
-      <c r="AO65" s="22"/>
-      <c r="AP65" s="22"/>
-      <c r="AQ65" s="22"/>
-      <c r="AR65" s="22"/>
-      <c r="AS65" s="22"/>
-      <c r="AT65" s="22"/>
-      <c r="AU65" s="22"/>
-      <c r="AV65" s="22"/>
-    </row>
-    <row r="66" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A66" s="22"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
-      <c r="I66" s="22"/>
-      <c r="J66" s="22"/>
-      <c r="K66" s="22"/>
-      <c r="L66" s="22"/>
-      <c r="M66" s="22"/>
-      <c r="N66" s="22"/>
-      <c r="O66" s="22"/>
-      <c r="P66" s="22"/>
-      <c r="Q66" s="22"/>
-      <c r="R66" s="22"/>
-      <c r="S66" s="22"/>
-      <c r="T66" s="22"/>
-      <c r="U66" s="22"/>
-      <c r="V66" s="22"/>
-      <c r="W66" s="22"/>
-      <c r="X66" s="22"/>
-      <c r="Y66" s="22"/>
-      <c r="Z66" s="22"/>
-      <c r="AA66" s="22"/>
-      <c r="AB66" s="22"/>
-      <c r="AC66" s="22"/>
-      <c r="AD66" s="22"/>
-      <c r="AE66" s="22"/>
-      <c r="AF66" s="22"/>
-      <c r="AG66" s="22"/>
-      <c r="AH66" s="22"/>
-      <c r="AI66" s="22"/>
-      <c r="AJ66" s="22"/>
-      <c r="AK66" s="22"/>
-      <c r="AL66" s="22"/>
-      <c r="AM66" s="22"/>
-      <c r="AN66" s="22"/>
-      <c r="AO66" s="22"/>
-      <c r="AP66" s="22"/>
-      <c r="AQ66" s="22"/>
-      <c r="AR66" s="22"/>
-      <c r="AS66" s="22"/>
-      <c r="AT66" s="22"/>
-      <c r="AU66" s="22"/>
-      <c r="AV66" s="22"/>
-    </row>
-    <row r="67" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A67" s="22"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="22"/>
-      <c r="K67" s="22"/>
-      <c r="L67" s="22"/>
-      <c r="M67" s="22"/>
-      <c r="N67" s="22"/>
-      <c r="O67" s="22"/>
-      <c r="P67" s="22"/>
-      <c r="Q67" s="22"/>
-      <c r="R67" s="22"/>
-      <c r="S67" s="22"/>
-      <c r="T67" s="22"/>
-      <c r="U67" s="22"/>
-      <c r="V67" s="22"/>
-      <c r="W67" s="22"/>
-      <c r="X67" s="22"/>
-      <c r="Y67" s="22"/>
-      <c r="Z67" s="22"/>
-      <c r="AA67" s="22"/>
-      <c r="AB67" s="22"/>
-      <c r="AC67" s="22"/>
-      <c r="AD67" s="22"/>
-      <c r="AE67" s="22"/>
-      <c r="AF67" s="22"/>
-      <c r="AG67" s="22"/>
-      <c r="AH67" s="22"/>
-      <c r="AI67" s="22"/>
-      <c r="AJ67" s="22"/>
-      <c r="AK67" s="22"/>
-      <c r="AL67" s="22"/>
-      <c r="AM67" s="22"/>
-      <c r="AN67" s="22"/>
-      <c r="AO67" s="22"/>
-      <c r="AP67" s="22"/>
-      <c r="AQ67" s="22"/>
-      <c r="AR67" s="22"/>
-      <c r="AS67" s="22"/>
-      <c r="AT67" s="22"/>
-      <c r="AU67" s="22"/>
-      <c r="AV67" s="22"/>
-    </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
-      <c r="L68" s="22"/>
-      <c r="M68" s="22"/>
-      <c r="N68" s="22"/>
-      <c r="O68" s="22"/>
-      <c r="P68" s="22"/>
-      <c r="Q68" s="22"/>
-      <c r="R68" s="22"/>
-      <c r="S68" s="22"/>
-      <c r="T68" s="22"/>
-      <c r="U68" s="22"/>
-      <c r="V68" s="22"/>
-      <c r="W68" s="22"/>
-      <c r="X68" s="22"/>
-      <c r="Y68" s="22"/>
-      <c r="Z68" s="22"/>
-      <c r="AA68" s="22"/>
-      <c r="AB68" s="22"/>
-      <c r="AC68" s="22"/>
-      <c r="AD68" s="22"/>
-      <c r="AE68" s="22"/>
-      <c r="AF68" s="22"/>
-      <c r="AG68" s="22"/>
-      <c r="AH68" s="22"/>
-      <c r="AI68" s="22"/>
-      <c r="AJ68" s="22"/>
-      <c r="AK68" s="22"/>
-      <c r="AL68" s="22"/>
-      <c r="AM68" s="22"/>
-      <c r="AN68" s="22"/>
-      <c r="AO68" s="22"/>
-      <c r="AP68" s="22"/>
-      <c r="AQ68" s="22"/>
-      <c r="AR68" s="22"/>
-      <c r="AS68" s="22"/>
-      <c r="AT68" s="22"/>
-      <c r="AU68" s="22"/>
-      <c r="AV68" s="22"/>
-    </row>
-    <row r="69" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A69" s="22"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="22"/>
-      <c r="K69" s="22"/>
-      <c r="L69" s="22"/>
-      <c r="M69" s="22"/>
-      <c r="N69" s="22"/>
-      <c r="O69" s="22"/>
-      <c r="P69" s="22"/>
-      <c r="Q69" s="22"/>
-      <c r="R69" s="22"/>
-      <c r="S69" s="22"/>
-      <c r="T69" s="22"/>
-      <c r="U69" s="22"/>
-      <c r="V69" s="22"/>
-      <c r="W69" s="22"/>
-      <c r="X69" s="22"/>
-      <c r="Y69" s="22"/>
-      <c r="Z69" s="22"/>
-      <c r="AA69" s="22"/>
-      <c r="AB69" s="22"/>
-      <c r="AC69" s="22"/>
-      <c r="AD69" s="22"/>
-      <c r="AE69" s="22"/>
-      <c r="AF69" s="22"/>
-      <c r="AG69" s="22"/>
-      <c r="AH69" s="22"/>
-      <c r="AI69" s="22"/>
-      <c r="AJ69" s="22"/>
-      <c r="AK69" s="22"/>
-      <c r="AL69" s="22"/>
-      <c r="AM69" s="22"/>
-      <c r="AN69" s="22"/>
-      <c r="AO69" s="22"/>
-      <c r="AP69" s="22"/>
-      <c r="AQ69" s="22"/>
-      <c r="AR69" s="22"/>
-      <c r="AS69" s="22"/>
-      <c r="AT69" s="22"/>
-      <c r="AU69" s="22"/>
-      <c r="AV69" s="22"/>
-    </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A70" s="22"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
-      <c r="L70" s="22"/>
-      <c r="M70" s="22"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="22"/>
-      <c r="P70" s="22"/>
-      <c r="Q70" s="22"/>
-      <c r="R70" s="22"/>
-      <c r="S70" s="22"/>
-      <c r="T70" s="22"/>
-      <c r="U70" s="22"/>
-      <c r="V70" s="22"/>
-      <c r="W70" s="22"/>
-      <c r="X70" s="22"/>
-      <c r="Y70" s="22"/>
-      <c r="Z70" s="22"/>
-      <c r="AA70" s="22"/>
-      <c r="AB70" s="22"/>
-      <c r="AC70" s="22"/>
-      <c r="AD70" s="22"/>
-      <c r="AE70" s="22"/>
-      <c r="AF70" s="22"/>
-      <c r="AG70" s="22"/>
-      <c r="AH70" s="22"/>
-      <c r="AI70" s="22"/>
-      <c r="AJ70" s="22"/>
-      <c r="AK70" s="22"/>
-      <c r="AL70" s="22"/>
-      <c r="AM70" s="22"/>
-      <c r="AN70" s="22"/>
-      <c r="AO70" s="22"/>
-      <c r="AP70" s="22"/>
-      <c r="AQ70" s="22"/>
-      <c r="AR70" s="22"/>
-      <c r="AS70" s="22"/>
-      <c r="AT70" s="22"/>
-      <c r="AU70" s="22"/>
-      <c r="AV70" s="22"/>
-    </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A71" s="22"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="22"/>
-      <c r="P71" s="22"/>
-      <c r="Q71" s="22"/>
-      <c r="R71" s="22"/>
-      <c r="S71" s="22"/>
-      <c r="T71" s="22"/>
-      <c r="U71" s="22"/>
-      <c r="V71" s="22"/>
-      <c r="W71" s="22"/>
-      <c r="X71" s="22"/>
-      <c r="Y71" s="22"/>
-      <c r="Z71" s="22"/>
-      <c r="AA71" s="22"/>
-      <c r="AB71" s="22"/>
-      <c r="AC71" s="22"/>
-      <c r="AD71" s="22"/>
-      <c r="AE71" s="22"/>
-      <c r="AF71" s="22"/>
-      <c r="AG71" s="22"/>
-      <c r="AH71" s="22"/>
-      <c r="AI71" s="22"/>
-      <c r="AJ71" s="22"/>
-      <c r="AK71" s="22"/>
-      <c r="AL71" s="22"/>
-      <c r="AM71" s="22"/>
-      <c r="AN71" s="22"/>
-      <c r="AO71" s="22"/>
-      <c r="AP71" s="22"/>
-      <c r="AQ71" s="22"/>
-      <c r="AR71" s="22"/>
-      <c r="AS71" s="22"/>
-      <c r="AT71" s="22"/>
-      <c r="AU71" s="22"/>
-      <c r="AV71" s="22"/>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A72" s="22"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="22"/>
-      <c r="K72" s="22"/>
-      <c r="L72" s="22"/>
-      <c r="M72" s="22"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="22"/>
-      <c r="P72" s="22"/>
-      <c r="Q72" s="22"/>
-      <c r="R72" s="22"/>
-      <c r="S72" s="22"/>
-      <c r="T72" s="22"/>
-      <c r="U72" s="22"/>
-      <c r="V72" s="22"/>
-      <c r="W72" s="22"/>
-      <c r="X72" s="22"/>
-      <c r="Y72" s="22"/>
-      <c r="Z72" s="22"/>
-      <c r="AA72" s="22"/>
-      <c r="AB72" s="22"/>
-      <c r="AC72" s="22"/>
-      <c r="AD72" s="22"/>
-      <c r="AE72" s="22"/>
-      <c r="AF72" s="22"/>
-      <c r="AG72" s="22"/>
-      <c r="AH72" s="22"/>
-      <c r="AI72" s="22"/>
-      <c r="AJ72" s="22"/>
-      <c r="AK72" s="22"/>
-      <c r="AL72" s="22"/>
-      <c r="AM72" s="22"/>
-      <c r="AN72" s="22"/>
-      <c r="AO72" s="22"/>
-      <c r="AP72" s="22"/>
-      <c r="AQ72" s="22"/>
-      <c r="AR72" s="22"/>
-      <c r="AS72" s="22"/>
-      <c r="AT72" s="22"/>
-      <c r="AU72" s="22"/>
-      <c r="AV72" s="22"/>
-    </row>
-    <row r="73" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A73" s="22"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="22"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
-      <c r="R73" s="22"/>
-      <c r="S73" s="22"/>
-      <c r="T73" s="22"/>
-      <c r="U73" s="22"/>
-      <c r="V73" s="22"/>
-      <c r="W73" s="22"/>
-      <c r="X73" s="22"/>
-      <c r="Y73" s="22"/>
-      <c r="Z73" s="22"/>
-      <c r="AA73" s="22"/>
-      <c r="AB73" s="22"/>
-      <c r="AC73" s="22"/>
-      <c r="AD73" s="22"/>
-      <c r="AE73" s="22"/>
-      <c r="AF73" s="22"/>
-      <c r="AG73" s="22"/>
-      <c r="AH73" s="22"/>
-      <c r="AI73" s="22"/>
-      <c r="AJ73" s="22"/>
-      <c r="AK73" s="22"/>
-      <c r="AL73" s="22"/>
-      <c r="AM73" s="22"/>
-      <c r="AN73" s="22"/>
-      <c r="AO73" s="22"/>
-      <c r="AP73" s="22"/>
-      <c r="AQ73" s="22"/>
-      <c r="AR73" s="22"/>
-      <c r="AS73" s="22"/>
-      <c r="AT73" s="22"/>
-      <c r="AU73" s="22"/>
-      <c r="AV73" s="22"/>
-    </row>
-    <row r="74" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A74" s="22"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="22"/>
-      <c r="L74" s="22"/>
-      <c r="M74" s="22"/>
-      <c r="N74" s="22"/>
-      <c r="O74" s="22"/>
-      <c r="P74" s="22"/>
-      <c r="Q74" s="22"/>
-      <c r="R74" s="22"/>
-      <c r="S74" s="22"/>
-      <c r="T74" s="22"/>
-      <c r="U74" s="22"/>
-      <c r="V74" s="22"/>
-      <c r="W74" s="22"/>
-      <c r="X74" s="22"/>
-      <c r="Y74" s="22"/>
-      <c r="Z74" s="22"/>
-      <c r="AA74" s="22"/>
-      <c r="AB74" s="22"/>
-      <c r="AC74" s="22"/>
-      <c r="AD74" s="22"/>
-      <c r="AE74" s="22"/>
-      <c r="AF74" s="22"/>
-      <c r="AG74" s="22"/>
-      <c r="AH74" s="22"/>
-      <c r="AI74" s="22"/>
-      <c r="AJ74" s="22"/>
-      <c r="AK74" s="22"/>
-      <c r="AL74" s="22"/>
-      <c r="AM74" s="22"/>
-      <c r="AN74" s="22"/>
-      <c r="AO74" s="22"/>
-      <c r="AP74" s="22"/>
-      <c r="AQ74" s="22"/>
-      <c r="AR74" s="22"/>
-      <c r="AS74" s="22"/>
-      <c r="AT74" s="22"/>
-      <c r="AU74" s="22"/>
-      <c r="AV74" s="22"/>
-    </row>
-    <row r="75" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A75" s="22"/>
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="22"/>
-      <c r="L75" s="22"/>
-      <c r="M75" s="22"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="22"/>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
-      <c r="T75" s="22"/>
-      <c r="U75" s="22"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="22"/>
-      <c r="X75" s="22"/>
-      <c r="Y75" s="22"/>
-      <c r="Z75" s="22"/>
-      <c r="AA75" s="22"/>
-      <c r="AB75" s="22"/>
-      <c r="AC75" s="22"/>
-      <c r="AD75" s="22"/>
-      <c r="AE75" s="22"/>
-      <c r="AF75" s="22"/>
-      <c r="AG75" s="22"/>
-      <c r="AH75" s="22"/>
-      <c r="AI75" s="22"/>
-      <c r="AJ75" s="22"/>
-      <c r="AK75" s="22"/>
-      <c r="AL75" s="22"/>
-      <c r="AM75" s="22"/>
-      <c r="AN75" s="22"/>
-      <c r="AO75" s="22"/>
-      <c r="AP75" s="22"/>
-      <c r="AQ75" s="22"/>
-      <c r="AR75" s="22"/>
-      <c r="AS75" s="22"/>
-      <c r="AT75" s="22"/>
-      <c r="AU75" s="22"/>
-      <c r="AV75" s="22"/>
-    </row>
-    <row r="76" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A76" s="22"/>
-      <c r="B76" s="22"/>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="22"/>
-      <c r="J76" s="22"/>
-      <c r="K76" s="22"/>
-      <c r="L76" s="22"/>
-      <c r="M76" s="22"/>
-      <c r="N76" s="22"/>
-      <c r="O76" s="22"/>
-      <c r="P76" s="22"/>
-      <c r="Q76" s="22"/>
-      <c r="R76" s="22"/>
-      <c r="S76" s="22"/>
-      <c r="T76" s="22"/>
-      <c r="U76" s="22"/>
-      <c r="V76" s="22"/>
-      <c r="W76" s="22"/>
-      <c r="X76" s="22"/>
-      <c r="Y76" s="22"/>
-      <c r="Z76" s="22"/>
-      <c r="AA76" s="22"/>
-      <c r="AB76" s="22"/>
-      <c r="AC76" s="22"/>
-      <c r="AD76" s="22"/>
-      <c r="AE76" s="22"/>
-      <c r="AF76" s="22"/>
-      <c r="AG76" s="22"/>
-      <c r="AH76" s="22"/>
-      <c r="AI76" s="22"/>
-      <c r="AJ76" s="22"/>
-      <c r="AK76" s="22"/>
-      <c r="AL76" s="22"/>
-      <c r="AM76" s="22"/>
-      <c r="AN76" s="22"/>
-      <c r="AO76" s="22"/>
-      <c r="AP76" s="22"/>
-      <c r="AQ76" s="22"/>
-      <c r="AR76" s="22"/>
-      <c r="AS76" s="22"/>
-      <c r="AT76" s="22"/>
-      <c r="AU76" s="22"/>
-      <c r="AV76" s="22"/>
-    </row>
-    <row r="77" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A77" s="22"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="22"/>
-      <c r="J77" s="22"/>
-      <c r="K77" s="22"/>
-      <c r="L77" s="22"/>
-      <c r="M77" s="22"/>
-      <c r="N77" s="22"/>
-      <c r="O77" s="22"/>
-      <c r="P77" s="22"/>
-      <c r="Q77" s="22"/>
-      <c r="R77" s="22"/>
-      <c r="S77" s="22"/>
-      <c r="T77" s="22"/>
-      <c r="U77" s="22"/>
-      <c r="V77" s="22"/>
-      <c r="W77" s="22"/>
-      <c r="X77" s="22"/>
-      <c r="Y77" s="22"/>
-      <c r="Z77" s="22"/>
-      <c r="AA77" s="22"/>
-      <c r="AB77" s="22"/>
-      <c r="AC77" s="22"/>
-      <c r="AD77" s="22"/>
-      <c r="AE77" s="22"/>
-      <c r="AF77" s="22"/>
-      <c r="AG77" s="22"/>
-      <c r="AH77" s="22"/>
-      <c r="AI77" s="22"/>
-      <c r="AJ77" s="22"/>
-      <c r="AK77" s="22"/>
-      <c r="AL77" s="22"/>
-      <c r="AM77" s="22"/>
-      <c r="AN77" s="22"/>
-      <c r="AO77" s="22"/>
-      <c r="AP77" s="22"/>
-      <c r="AQ77" s="22"/>
-      <c r="AR77" s="22"/>
-      <c r="AS77" s="22"/>
-      <c r="AT77" s="22"/>
-      <c r="AU77" s="22"/>
-      <c r="AV77" s="22"/>
-    </row>
-    <row r="78" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A78" s="22"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
-      <c r="G78" s="22"/>
-      <c r="H78" s="22"/>
-      <c r="I78" s="22"/>
-      <c r="J78" s="22"/>
-      <c r="K78" s="22"/>
-      <c r="L78" s="22"/>
-      <c r="M78" s="22"/>
-      <c r="N78" s="22"/>
-      <c r="O78" s="22"/>
-      <c r="P78" s="22"/>
-      <c r="Q78" s="22"/>
-      <c r="R78" s="22"/>
-      <c r="S78" s="22"/>
-      <c r="T78" s="22"/>
-      <c r="U78" s="22"/>
-      <c r="V78" s="22"/>
-      <c r="W78" s="22"/>
-      <c r="X78" s="22"/>
-      <c r="Y78" s="22"/>
-      <c r="Z78" s="22"/>
-      <c r="AA78" s="22"/>
-      <c r="AB78" s="22"/>
-      <c r="AC78" s="22"/>
-      <c r="AD78" s="22"/>
-      <c r="AE78" s="22"/>
-      <c r="AF78" s="22"/>
-      <c r="AG78" s="22"/>
-      <c r="AH78" s="22"/>
-      <c r="AI78" s="22"/>
-      <c r="AJ78" s="22"/>
-      <c r="AK78" s="22"/>
-      <c r="AL78" s="22"/>
-      <c r="AM78" s="22"/>
-      <c r="AN78" s="22"/>
-      <c r="AO78" s="22"/>
-      <c r="AP78" s="22"/>
-      <c r="AQ78" s="22"/>
-      <c r="AR78" s="22"/>
-      <c r="AS78" s="22"/>
-      <c r="AT78" s="22"/>
-      <c r="AU78" s="22"/>
-      <c r="AV78" s="22"/>
-    </row>
-    <row r="79" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A79" s="22"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
-      <c r="G79" s="22"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="22"/>
-      <c r="K79" s="22"/>
-      <c r="L79" s="22"/>
-      <c r="M79" s="22"/>
-      <c r="N79" s="22"/>
-      <c r="O79" s="22"/>
-      <c r="P79" s="22"/>
-      <c r="Q79" s="22"/>
-      <c r="R79" s="22"/>
-      <c r="S79" s="22"/>
-      <c r="T79" s="22"/>
-      <c r="U79" s="22"/>
-      <c r="V79" s="22"/>
-      <c r="W79" s="22"/>
-      <c r="X79" s="22"/>
-      <c r="Y79" s="22"/>
-      <c r="Z79" s="22"/>
-      <c r="AA79" s="22"/>
-      <c r="AB79" s="22"/>
-      <c r="AC79" s="22"/>
-      <c r="AD79" s="22"/>
-      <c r="AE79" s="22"/>
-      <c r="AF79" s="22"/>
-      <c r="AG79" s="22"/>
-      <c r="AH79" s="22"/>
-      <c r="AI79" s="22"/>
-      <c r="AJ79" s="22"/>
-      <c r="AK79" s="22"/>
-      <c r="AL79" s="22"/>
-      <c r="AM79" s="22"/>
-      <c r="AN79" s="22"/>
-      <c r="AO79" s="22"/>
-      <c r="AP79" s="22"/>
-      <c r="AQ79" s="22"/>
-      <c r="AR79" s="22"/>
-      <c r="AS79" s="22"/>
-      <c r="AT79" s="22"/>
-      <c r="AU79" s="22"/>
-      <c r="AV79" s="22"/>
-    </row>
-    <row r="80" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A80" s="22"/>
-      <c r="B80" s="22"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="22"/>
-      <c r="L80" s="22"/>
-      <c r="M80" s="22"/>
-      <c r="N80" s="22"/>
-      <c r="O80" s="22"/>
-      <c r="P80" s="22"/>
-      <c r="Q80" s="22"/>
-      <c r="R80" s="22"/>
-      <c r="S80" s="22"/>
-      <c r="T80" s="22"/>
-      <c r="U80" s="22"/>
-      <c r="V80" s="22"/>
-      <c r="W80" s="22"/>
-      <c r="X80" s="22"/>
-      <c r="Y80" s="22"/>
-      <c r="Z80" s="22"/>
-      <c r="AA80" s="22"/>
-      <c r="AB80" s="22"/>
-      <c r="AC80" s="22"/>
-      <c r="AD80" s="22"/>
-      <c r="AE80" s="22"/>
-      <c r="AF80" s="22"/>
-      <c r="AG80" s="22"/>
-      <c r="AH80" s="22"/>
-      <c r="AI80" s="22"/>
-      <c r="AJ80" s="22"/>
-      <c r="AK80" s="22"/>
-      <c r="AL80" s="22"/>
-      <c r="AM80" s="22"/>
-      <c r="AN80" s="22"/>
-      <c r="AO80" s="22"/>
-      <c r="AP80" s="22"/>
-      <c r="AQ80" s="22"/>
-      <c r="AR80" s="22"/>
-      <c r="AS80" s="22"/>
-      <c r="AT80" s="22"/>
-      <c r="AU80" s="22"/>
-      <c r="AV80" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
